--- a/prisma/data/estructura_bd.xlsx
+++ b/prisma/data/estructura_bd.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBE2063F-B5B5-4E52-96AB-65765A2444E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" firstSheet="6" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="📌 Índice" sheetId="1" r:id="rId1"/>
@@ -2358,20 +2358,20 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2397,6 +2397,83 @@
         <bottom style="thin">
           <color rgb="FFAAAAAA"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -2426,7 +2503,50 @@
         <left style="thin">
           <color rgb="FFAAAAAA"/>
         </left>
-        <right/>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
         <top style="thin">
           <color rgb="FFAAAAAA"/>
         </top>
@@ -2500,7 +2620,44 @@
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FFAAAAAA"/>
         </left>
@@ -2513,8 +2670,6 @@
         <bottom style="thin">
           <color rgb="FFAAAAAA"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -2540,61 +2695,17 @@
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FFAAAAAA"/>
         </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
+        <right/>
         <top style="thin">
           <color rgb="FFAAAAAA"/>
         </top>
         <bottom style="thin">
           <color rgb="FFAAAAAA"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -5515,51 +5626,12 @@
           <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color rgb="FFAAAAAA"/>
         </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
+        <right/>
         <top style="thin">
           <color rgb="FFAAAAAA"/>
         </top>
@@ -5626,7 +5698,6 @@
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -5714,8 +5785,10 @@
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
         <right style="thin">
           <color rgb="FFAAAAAA"/>
         </right>
@@ -5725,81 +5798,8 @@
         <bottom style="thin">
           <color rgb="FFAAAAAA"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -5971,58 +5971,58 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{21BDF646-6AB5-43B7-AD3B-7DFA6765727B}" name="ADegreeTable" displayName="ADegreeTable" ref="A6:B8" totalsRowShown="0" headerRowDxfId="105" headerRowBorderDxfId="104" tableBorderDxfId="103" totalsRowBorderDxfId="102">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{21BDF646-6AB5-43B7-AD3B-7DFA6765727B}" name="ADegreeTable" displayName="ADegreeTable" ref="A6:B8" totalsRowShown="0" headerRowDxfId="108" headerRowBorderDxfId="107" tableBorderDxfId="106" totalsRowBorderDxfId="105">
   <autoFilter ref="A6:B8" xr:uid="{21BDF646-6AB5-43B7-AD3B-7DFA6765727B}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{D084344C-E421-48F0-8ED9-9638F88C6846}" name="id"/>
-    <tableColumn id="2" xr3:uid="{9F0DCB94-4F04-48E3-B0C1-197AD7B74B6B}" name="name" dataDxfId="101"/>
+    <tableColumn id="2" xr3:uid="{9F0DCB94-4F04-48E3-B0C1-197AD7B74B6B}" name="name" dataDxfId="104"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{7B666A61-9D82-4C49-BCCD-2E916244936B}" name="TemplateTable" displayName="TemplateTable" ref="A6:I11" totalsRowShown="0" headerRowDxfId="119" dataDxfId="117" headerRowBorderDxfId="118" tableBorderDxfId="116" totalsRowBorderDxfId="115">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{7B666A61-9D82-4C49-BCCD-2E916244936B}" name="TemplateTable" displayName="TemplateTable" ref="A6:I11" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13" totalsRowBorderDxfId="12">
   <autoFilter ref="A6:I11" xr:uid="{7B666A61-9D82-4C49-BCCD-2E916244936B}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{35DFD295-E223-4974-ACE2-697935223713}" name="id" dataDxfId="114">
+    <tableColumn id="1" xr3:uid="{35DFD295-E223-4974-ACE2-697935223713}" name="id" dataDxfId="11">
       <calculatedColumnFormula>IF(ISBLANK(TemplateTable[[#This Row],[certificateName]]),"",ROW()-6)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F0014E9D-997A-4846-891A-BB433D709D81}" name="certificateName" dataDxfId="113"/>
-    <tableColumn id="3" xr3:uid="{6800626F-D286-415C-A674-0DB3C1DB73C2}" name="certificateId" dataDxfId="112">
+    <tableColumn id="2" xr3:uid="{F0014E9D-997A-4846-891A-BB433D709D81}" name="certificateName" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{6800626F-D286-415C-A674-0DB3C1DB73C2}" name="certificateId" dataDxfId="9">
       <calculatedColumnFormula>_xlfn.XLOOKUP(TemplateTable[[#This Row],[certificateName]],CertificateTable[name], CertificateTable[id],"",0,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{98120E82-B208-4584-AA36-331D4263F344}" name="role" dataDxfId="111"/>
-    <tableColumn id="8" xr3:uid="{1EC5D45E-1355-4169-9B29-F2DD20E04EC2}" name="activityTypeName" dataDxfId="110"/>
-    <tableColumn id="5" xr3:uid="{BFE3FA6C-D650-450B-9013-3E601CEFEAB9}" name="activityTypeId" dataDxfId="109">
+    <tableColumn id="4" xr3:uid="{98120E82-B208-4584-AA36-331D4263F344}" name="role" dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{1EC5D45E-1355-4169-9B29-F2DD20E04EC2}" name="activityTypeName" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{BFE3FA6C-D650-450B-9013-3E601CEFEAB9}" name="activityTypeId" dataDxfId="6">
       <calculatedColumnFormula>_xlfn.XLOOKUP(TemplateTable[[#This Row],[activityTypeName]], ActivityTypeTable[name],ActivityTypeTable[id], "",0,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{D2A34400-809B-4181-B7DE-643FA4E237AC}" name="participantTypeName" dataDxfId="108"/>
-    <tableColumn id="6" xr3:uid="{C114DF71-6DF2-480D-932F-564F087EDE4D}" name="participantTypeId" dataDxfId="107">
+    <tableColumn id="9" xr3:uid="{D2A34400-809B-4181-B7DE-643FA4E237AC}" name="participantTypeName" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{C114DF71-6DF2-480D-932F-564F087EDE4D}" name="participantTypeId" dataDxfId="4">
       <calculatedColumnFormula>_xlfn.XLOOKUP(TemplateTable[[#This Row],[participantTypeName]], ParticipantTypeTable[name], ParticipantTypeTable[id],"",0,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{718F385C-1FA2-47C7-A2A8-851AF99822CD}" name="template" dataDxfId="106"/>
+    <tableColumn id="7" xr3:uid="{718F385C-1FA2-47C7-A2A8-851AF99822CD}" name="template" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BC5C6D74-FC52-47E2-AA34-D6697409B949}" name="ExamTable" displayName="ExamTable" ref="A6:F7" totalsRowShown="0" headerRowDxfId="13" dataDxfId="11" headerRowBorderDxfId="12" tableBorderDxfId="10" totalsRowBorderDxfId="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BC5C6D74-FC52-47E2-AA34-D6697409B949}" name="ExamTable" displayName="ExamTable" ref="A6:F7" totalsRowShown="0" headerRowDxfId="119" dataDxfId="117" headerRowBorderDxfId="118" tableBorderDxfId="116" totalsRowBorderDxfId="115">
   <autoFilter ref="A6:F7" xr:uid="{BC5C6D74-FC52-47E2-AA34-D6697409B949}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{692719ED-79B2-42F7-9EE5-149A32F745B3}" name="id" dataDxfId="8">
+    <tableColumn id="1" xr3:uid="{692719ED-79B2-42F7-9EE5-149A32F745B3}" name="id" dataDxfId="114">
       <calculatedColumnFormula>IF(ISBLANK(ExamTable[[#This Row],[studentName]]),"",ROW()-6)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1B246D39-0161-43B5-A25E-5F63C4AE1C13}" name="studentName" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{9CA5A4E7-4070-4BCC-8ABE-22A888226F06}" name="activityName" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{21CCAFCC-797A-43FF-B871-B5CE4FD3B169}" name="studentId" dataDxfId="5">
+    <tableColumn id="2" xr3:uid="{1B246D39-0161-43B5-A25E-5F63C4AE1C13}" name="studentName" dataDxfId="113"/>
+    <tableColumn id="3" xr3:uid="{9CA5A4E7-4070-4BCC-8ABE-22A888226F06}" name="activityName" dataDxfId="112"/>
+    <tableColumn id="4" xr3:uid="{21CCAFCC-797A-43FF-B871-B5CE4FD3B169}" name="studentId" dataDxfId="111">
       <calculatedColumnFormula>_xlfn.XLOOKUP(ExamTable[[#This Row],[studentName]],StudentTable[userName],StudentTable[id],"",0,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6E4D44FF-C970-45A8-9C7A-5AE471194553}" name="activityId" dataDxfId="4">
+    <tableColumn id="5" xr3:uid="{6E4D44FF-C970-45A8-9C7A-5AE471194553}" name="activityId" dataDxfId="110">
       <calculatedColumnFormula>_xlfn.XLOOKUP(ExamTable[[#This Row],[activityName]],ActivityTable[name], ActivityTable[id],"",0,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{9C8DA54A-7DAD-473A-A016-641BD60DCBEA}" name="grade" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{9C8DA54A-7DAD-473A-A016-641BD60DCBEA}" name="grade" dataDxfId="109"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6048,41 +6048,41 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{1D06504D-941D-4F95-A34D-8031062A23F0}" name="TitleTable" displayName="TitleTable" ref="A6:E12" totalsRowShown="0" headerRowDxfId="100" headerRowBorderDxfId="99" tableBorderDxfId="98" totalsRowBorderDxfId="97">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{1D06504D-941D-4F95-A34D-8031062A23F0}" name="TitleTable" displayName="TitleTable" ref="A6:E12" totalsRowShown="0" headerRowDxfId="103" headerRowBorderDxfId="102" tableBorderDxfId="101" totalsRowBorderDxfId="100">
   <autoFilter ref="A6:E12" xr:uid="{1D06504D-941D-4F95-A34D-8031062A23F0}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{7801D28A-9FC1-4168-B38F-EE639910650A}" name="id" dataDxfId="96">
+    <tableColumn id="1" xr3:uid="{7801D28A-9FC1-4168-B38F-EE639910650A}" name="id" dataDxfId="99">
       <calculatedColumnFormula>IF(TitleTable[[#This Row],[academicDegreeId]]&lt;&gt;"",ROW()-6,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A7BC7DF6-3102-4BBA-BC51-DB8410EAB5BD}" name="academicDegreeId" dataDxfId="95">
+    <tableColumn id="2" xr3:uid="{A7BC7DF6-3102-4BBA-BC51-DB8410EAB5BD}" name="academicDegreeId" dataDxfId="98">
       <calculatedColumnFormula>_xlfn.XLOOKUP(TitleTable[[#This Row],[AcademicDegreeName]],ADegreeTable[name], ADegreeTable[id],"",0,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{A4F7459D-7F69-4F60-BB9E-B23C34251DCF}" name="AcademicDegreeName" dataDxfId="94"/>
-    <tableColumn id="3" xr3:uid="{300E313B-FA95-4376-9612-7FF1A398FA49}" name="gender" dataDxfId="93"/>
-    <tableColumn id="4" xr3:uid="{30F0397B-1916-4C7E-B449-91C6BCF48ADA}" name="abbrev" dataDxfId="92"/>
+    <tableColumn id="6" xr3:uid="{A4F7459D-7F69-4F60-BB9E-B23C34251DCF}" name="AcademicDegreeName" dataDxfId="97"/>
+    <tableColumn id="3" xr3:uid="{300E313B-FA95-4376-9612-7FF1A398FA49}" name="gender" dataDxfId="96"/>
+    <tableColumn id="4" xr3:uid="{30F0397B-1916-4C7E-B449-91C6BCF48ADA}" name="abbrev" dataDxfId="95"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{85FEA289-536E-4259-A619-2744ADA3DB87}" name="UserTable" displayName="UserTable" ref="A6:N36" totalsRowShown="0" headerRowDxfId="91" dataDxfId="90" tableBorderDxfId="89">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{85FEA289-536E-4259-A619-2744ADA3DB87}" name="UserTable" displayName="UserTable" ref="A6:N36" totalsRowShown="0" headerRowDxfId="94" dataDxfId="93" tableBorderDxfId="92">
   <autoFilter ref="A6:N36" xr:uid="{85FEA289-536E-4259-A619-2744ADA3DB87}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{D84565A3-15A3-40D5-885B-59C4991B2454}" name="id" dataDxfId="88">
+    <tableColumn id="1" xr3:uid="{D84565A3-15A3-40D5-885B-59C4991B2454}" name="id" dataDxfId="91">
       <calculatedColumnFormula>IF(UserTable[[#This Row],[rut]]&lt;&gt;"", ROW()-6,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{E789B167-226C-420B-BBD4-8755387CAFE6}" name="rut" dataDxfId="87"/>
-    <tableColumn id="3" xr3:uid="{93B4A9A1-DC9A-44FA-8692-C9A24CC1BF40}" name="name" dataDxfId="86"/>
-    <tableColumn id="4" xr3:uid="{63AB093F-B349-4655-86C2-B260E78F6BF1}" name="email" dataDxfId="85"/>
-    <tableColumn id="5" xr3:uid="{56D0A7C0-F001-4955-A153-E7F45CC5AF52}" name="emailVerified" dataDxfId="84"/>
-    <tableColumn id="6" xr3:uid="{7D04D1EC-A119-48D6-AD1F-240337054887}" name="image" dataDxfId="83"/>
-    <tableColumn id="7" xr3:uid="{CF3A91BB-659C-4083-935E-AFC637FBA3F3}" name="role" dataDxfId="82"/>
-    <tableColumn id="8" xr3:uid="{5C06DE85-13EF-4A5C-B6DB-B75E5FFC0545}" name="banned" dataDxfId="81"/>
-    <tableColumn id="9" xr3:uid="{8BFEF23D-7870-4777-A520-8246B3DE2FDF}" name="banReason" dataDxfId="80"/>
-    <tableColumn id="10" xr3:uid="{F672B4C8-D389-49C1-9B64-DE4E88445A59}" name="banExpires" dataDxfId="79"/>
-    <tableColumn id="11" xr3:uid="{90307C6C-1290-4627-8E69-FF7293A360C8}" name="gender" dataDxfId="78"/>
-    <tableColumn id="12" xr3:uid="{AFFA8672-1495-4235-9B93-04970AC93F2A}" name="isDirector" dataDxfId="77"/>
+    <tableColumn id="2" xr3:uid="{E789B167-226C-420B-BBD4-8755387CAFE6}" name="rut" dataDxfId="90"/>
+    <tableColumn id="3" xr3:uid="{93B4A9A1-DC9A-44FA-8692-C9A24CC1BF40}" name="name" dataDxfId="89"/>
+    <tableColumn id="4" xr3:uid="{63AB093F-B349-4655-86C2-B260E78F6BF1}" name="email" dataDxfId="88"/>
+    <tableColumn id="5" xr3:uid="{56D0A7C0-F001-4955-A153-E7F45CC5AF52}" name="emailVerified" dataDxfId="87"/>
+    <tableColumn id="6" xr3:uid="{7D04D1EC-A119-48D6-AD1F-240337054887}" name="image" dataDxfId="86"/>
+    <tableColumn id="7" xr3:uid="{CF3A91BB-659C-4083-935E-AFC637FBA3F3}" name="role" dataDxfId="85"/>
+    <tableColumn id="8" xr3:uid="{5C06DE85-13EF-4A5C-B6DB-B75E5FFC0545}" name="banned" dataDxfId="84"/>
+    <tableColumn id="9" xr3:uid="{8BFEF23D-7870-4777-A520-8246B3DE2FDF}" name="banReason" dataDxfId="83"/>
+    <tableColumn id="10" xr3:uid="{F672B4C8-D389-49C1-9B64-DE4E88445A59}" name="banExpires" dataDxfId="82"/>
+    <tableColumn id="11" xr3:uid="{90307C6C-1290-4627-8E69-FF7293A360C8}" name="gender" dataDxfId="81"/>
+    <tableColumn id="12" xr3:uid="{AFFA8672-1495-4235-9B93-04970AC93F2A}" name="isDirector" dataDxfId="80"/>
     <tableColumn id="13" xr3:uid="{623D3833-0700-46BB-9F79-F1EBAFC81D6A}" name="academicDegreeId">
       <calculatedColumnFormula>_xlfn.XLOOKUP(UserTable[[#This Row],[academicDegreeName]], ADegreeTable[name], ADegreeTable[id],"",0,1)</calculatedColumnFormula>
     </tableColumn>
@@ -6093,111 +6093,111 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{FCF25C97-1CFC-458F-A99C-18D9A6AD8A69}" name="StudentTable" displayName="StudentTable" ref="A6:F31" totalsRowShown="0" headerRowDxfId="76" dataDxfId="74" headerRowBorderDxfId="75" tableBorderDxfId="73" totalsRowBorderDxfId="72">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{FCF25C97-1CFC-458F-A99C-18D9A6AD8A69}" name="StudentTable" displayName="StudentTable" ref="A6:F31" totalsRowShown="0" headerRowDxfId="79" dataDxfId="77" headerRowBorderDxfId="78" tableBorderDxfId="76" totalsRowBorderDxfId="75">
   <autoFilter ref="A6:F31" xr:uid="{FCF25C97-1CFC-458F-A99C-18D9A6AD8A69}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{4365B9E5-05D3-43F2-9E75-34DB73C72A3F}" name="id" dataDxfId="71">
+    <tableColumn id="1" xr3:uid="{4365B9E5-05D3-43F2-9E75-34DB73C72A3F}" name="id" dataDxfId="74">
       <calculatedColumnFormula>IF(ISBLANK(StudentTable[[#This Row],[studentId]]),"", ROW()-6)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{EAC8744D-1F09-4A5C-8E4A-3D85E08B6D37}" name="studentId" dataDxfId="70"/>
-    <tableColumn id="3" xr3:uid="{66B37519-AF27-4C0F-9BFE-4DE89E499C64}" name="userName" dataDxfId="69"/>
-    <tableColumn id="4" xr3:uid="{76391975-9083-4AF9-B31F-55AE28819CFB}" name="userId" dataDxfId="68">
+    <tableColumn id="2" xr3:uid="{EAC8744D-1F09-4A5C-8E4A-3D85E08B6D37}" name="studentId" dataDxfId="73"/>
+    <tableColumn id="3" xr3:uid="{66B37519-AF27-4C0F-9BFE-4DE89E499C64}" name="userName" dataDxfId="72"/>
+    <tableColumn id="4" xr3:uid="{76391975-9083-4AF9-B31F-55AE28819CFB}" name="userId" dataDxfId="71">
       <calculatedColumnFormula>_xlfn.XLOOKUP(StudentTable[[#This Row],[userName]],UserTable[name],UserTable[id],"",0,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{BD538411-70FF-493E-B572-8105AB255D28}" name="isRegularStudent" dataDxfId="67"/>
-    <tableColumn id="6" xr3:uid="{D2EBA512-F8A8-4CB6-8EA2-A0DC38CB5C0B}" name="admisionDate" dataDxfId="66"/>
+    <tableColumn id="5" xr3:uid="{BD538411-70FF-493E-B572-8105AB255D28}" name="isRegularStudent" dataDxfId="70"/>
+    <tableColumn id="6" xr3:uid="{D2EBA512-F8A8-4CB6-8EA2-A0DC38CB5C0B}" name="admisionDate" dataDxfId="69"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{0F547C4C-61C7-4C2A-9C4D-C8523461AAFF}" name="ActivityTypeTable" displayName="ActivityTypeTable" ref="A6:B13" totalsRowShown="0" headerRowDxfId="65" headerRowBorderDxfId="64" tableBorderDxfId="63" totalsRowBorderDxfId="62">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{0F547C4C-61C7-4C2A-9C4D-C8523461AAFF}" name="ActivityTypeTable" displayName="ActivityTypeTable" ref="A6:B13" totalsRowShown="0" headerRowDxfId="68" headerRowBorderDxfId="67" tableBorderDxfId="66" totalsRowBorderDxfId="65">
   <autoFilter ref="A6:B13" xr:uid="{0F547C4C-61C7-4C2A-9C4D-C8523461AAFF}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{59150BA5-A7DE-4874-BEC8-662316686ECE}" name="id" dataDxfId="61">
+    <tableColumn id="1" xr3:uid="{59150BA5-A7DE-4874-BEC8-662316686ECE}" name="id" dataDxfId="64">
       <calculatedColumnFormula>IF(ISBLANK(ActivityTypeTable[[#This Row],[name]]),"", ROW()-6)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C734BFB6-8090-4FE5-B857-573748EB0614}" name="name" dataDxfId="60"/>
+    <tableColumn id="2" xr3:uid="{C734BFB6-8090-4FE5-B857-573748EB0614}" name="name" dataDxfId="63"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{DF67C1A1-6942-4B9F-AE16-A9B361C53B1A}" name="ActivityTable" displayName="ActivityTable" ref="A6:H7" totalsRowShown="0" headerRowDxfId="59" dataDxfId="57" headerRowBorderDxfId="58" tableBorderDxfId="56" totalsRowBorderDxfId="55">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{DF67C1A1-6942-4B9F-AE16-A9B361C53B1A}" name="ActivityTable" displayName="ActivityTable" ref="A6:H7" totalsRowShown="0" headerRowDxfId="62" dataDxfId="60" headerRowBorderDxfId="61" tableBorderDxfId="59" totalsRowBorderDxfId="58">
   <autoFilter ref="A6:H7" xr:uid="{DF67C1A1-6942-4B9F-AE16-A9B361C53B1A}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{ED578E86-4E76-4E90-85CA-674930C235F7}" name="id" dataDxfId="54"/>
-    <tableColumn id="2" xr3:uid="{FB6C5FA6-DF04-45A7-89B5-88F1FC79C2D6}" name="activityTypeName" dataDxfId="53"/>
-    <tableColumn id="3" xr3:uid="{EE938535-FAD5-46E2-9062-D0D81D92843E}" name="activityTypeId" dataDxfId="52">
+    <tableColumn id="1" xr3:uid="{ED578E86-4E76-4E90-85CA-674930C235F7}" name="id" dataDxfId="57"/>
+    <tableColumn id="2" xr3:uid="{FB6C5FA6-DF04-45A7-89B5-88F1FC79C2D6}" name="activityTypeName" dataDxfId="56"/>
+    <tableColumn id="3" xr3:uid="{EE938535-FAD5-46E2-9062-D0D81D92843E}" name="activityTypeId" dataDxfId="55">
       <calculatedColumnFormula>_xlfn.XLOOKUP(ActivityTable[[#This Row],[activityTypeName]],ActivityTypeTable[name], ActivityTypeTable[id],"",0,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{7E99DBF1-B701-4269-8285-40CB77EE77CF}" name="name" dataDxfId="51"/>
-    <tableColumn id="5" xr3:uid="{3F2225E0-5303-4D1E-95EC-65F1B96512C6}" name="startAt" dataDxfId="50"/>
-    <tableColumn id="6" xr3:uid="{D19CBEFD-D71A-41F7-A14B-DF9F5A8E0CA5}" name="endAt" dataDxfId="49"/>
-    <tableColumn id="7" xr3:uid="{A77D4338-9AE4-4919-BC5C-02F7DEF383DE}" name="nAssistant" dataDxfId="48"/>
-    <tableColumn id="8" xr3:uid="{AB81B6E6-2917-4082-9767-BA28157B6C97}" name="nParticipant" dataDxfId="47"/>
+    <tableColumn id="4" xr3:uid="{7E99DBF1-B701-4269-8285-40CB77EE77CF}" name="name" dataDxfId="54"/>
+    <tableColumn id="5" xr3:uid="{3F2225E0-5303-4D1E-95EC-65F1B96512C6}" name="startAt" dataDxfId="53"/>
+    <tableColumn id="6" xr3:uid="{D19CBEFD-D71A-41F7-A14B-DF9F5A8E0CA5}" name="endAt" dataDxfId="52"/>
+    <tableColumn id="7" xr3:uid="{A77D4338-9AE4-4919-BC5C-02F7DEF383DE}" name="nAssistant" dataDxfId="51"/>
+    <tableColumn id="8" xr3:uid="{AB81B6E6-2917-4082-9767-BA28157B6C97}" name="nParticipant" dataDxfId="50"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{23ADF508-CC90-4FBB-B8A6-80FFBB135690}" name="ParticipantTypeTable" displayName="ParticipantTypeTable" ref="A6:G22" totalsRowShown="0" headerRowDxfId="46" dataDxfId="44" headerRowBorderDxfId="45" tableBorderDxfId="43" totalsRowBorderDxfId="42">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{23ADF508-CC90-4FBB-B8A6-80FFBB135690}" name="ParticipantTypeTable" displayName="ParticipantTypeTable" ref="A6:G22" totalsRowShown="0" headerRowDxfId="49" dataDxfId="47" headerRowBorderDxfId="48" tableBorderDxfId="46" totalsRowBorderDxfId="45">
   <autoFilter ref="A6:G22" xr:uid="{23ADF508-CC90-4FBB-B8A6-80FFBB135690}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{10A749B4-38CA-4B67-A4C5-C561F90DDDE2}" name="id" dataDxfId="41">
+    <tableColumn id="1" xr3:uid="{10A749B4-38CA-4B67-A4C5-C561F90DDDE2}" name="id" dataDxfId="44">
       <calculatedColumnFormula>IF(ISBLANK(ParticipantTypeTable[[#This Row],[name]]),"", ROW()-6)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{04AFB6EC-E691-421A-B26F-9891A42D291E}" name="name" dataDxfId="40"/>
-    <tableColumn id="3" xr3:uid="{12DF8505-E053-492C-8C45-4D52788AA007}" name="roles" dataDxfId="39"/>
-    <tableColumn id="4" xr3:uid="{D684A6E0-2CB6-43AD-AA2A-978621E5D4DB}" name="activityTypeName" dataDxfId="38"/>
-    <tableColumn id="5" xr3:uid="{8BB7BDF5-9C51-428B-8F41-2D5551800DA8}" name="activityTypeId" dataDxfId="37">
+    <tableColumn id="2" xr3:uid="{04AFB6EC-E691-421A-B26F-9891A42D291E}" name="name" dataDxfId="43"/>
+    <tableColumn id="3" xr3:uid="{12DF8505-E053-492C-8C45-4D52788AA007}" name="roles" dataDxfId="42"/>
+    <tableColumn id="4" xr3:uid="{D684A6E0-2CB6-43AD-AA2A-978621E5D4DB}" name="activityTypeName" dataDxfId="41"/>
+    <tableColumn id="5" xr3:uid="{8BB7BDF5-9C51-428B-8F41-2D5551800DA8}" name="activityTypeId" dataDxfId="40">
       <calculatedColumnFormula>_xlfn.XLOOKUP(ParticipantTypeTable[[#This Row],[activityTypeName]],ActivityTypeTable[name], ActivityTypeTable[id],"",0,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{D21DFADD-72C9-48EF-9B97-94DCE941715E}" name=" min" dataDxfId="36"/>
-    <tableColumn id="9" xr3:uid="{2EB78418-4933-4BE7-848D-737A5AED6CD7}" name="max" dataDxfId="35"/>
+    <tableColumn id="8" xr3:uid="{D21DFADD-72C9-48EF-9B97-94DCE941715E}" name=" min" dataDxfId="39"/>
+    <tableColumn id="9" xr3:uid="{2EB78418-4933-4BE7-848D-737A5AED6CD7}" name="max" dataDxfId="38"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{15FD7229-441E-4FE3-AF45-908EA33D6E1A}" name="ParticipantTable" displayName="ParticipantTable" ref="A6:J7" totalsRowShown="0" headerRowDxfId="34" dataDxfId="32" headerRowBorderDxfId="33" tableBorderDxfId="31" totalsRowBorderDxfId="30">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{15FD7229-441E-4FE3-AF45-908EA33D6E1A}" name="ParticipantTable" displayName="ParticipantTable" ref="A6:J7" totalsRowShown="0" headerRowDxfId="37" dataDxfId="35" headerRowBorderDxfId="36" tableBorderDxfId="34" totalsRowBorderDxfId="33">
   <autoFilter ref="A6:J7" xr:uid="{15FD7229-441E-4FE3-AF45-908EA33D6E1A}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{652686EA-7035-4724-9CDA-D89B37DDB77D}" name="id" dataDxfId="29">
+    <tableColumn id="1" xr3:uid="{652686EA-7035-4724-9CDA-D89B37DDB77D}" name="id" dataDxfId="32">
       <calculatedColumnFormula>IF(ISBLANK(ParticipantTable[[#This Row],[activityName]]),"", ROW()-6)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{394ADFAF-FF0E-462F-BF79-96D9AFAC3CEA}" name="activityName" dataDxfId="28"/>
-    <tableColumn id="3" xr3:uid="{8FD18E64-E7FA-44AD-A7EC-413A12C07581}" name="userName" dataDxfId="27"/>
-    <tableColumn id="4" xr3:uid="{343F771A-82D0-4DC1-900F-370A7B1BECD0}" name="participantTypeName" dataDxfId="26"/>
-    <tableColumn id="5" xr3:uid="{BE01A539-C086-41E4-9971-BA82DB1D694F}" name="activityId" dataDxfId="25">
+    <tableColumn id="2" xr3:uid="{394ADFAF-FF0E-462F-BF79-96D9AFAC3CEA}" name="activityName" dataDxfId="31"/>
+    <tableColumn id="3" xr3:uid="{8FD18E64-E7FA-44AD-A7EC-413A12C07581}" name="userName" dataDxfId="30"/>
+    <tableColumn id="4" xr3:uid="{343F771A-82D0-4DC1-900F-370A7B1BECD0}" name="participantTypeName" dataDxfId="29"/>
+    <tableColumn id="5" xr3:uid="{BE01A539-C086-41E4-9971-BA82DB1D694F}" name="activityId" dataDxfId="28">
       <calculatedColumnFormula>_xlfn.XLOOKUP(ParticipantTable[[#This Row],[activityName]],ActivityTable[name], ActivityTable[id],"",0,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{0A7CDBA9-FD84-4CC8-8EDF-CD8D694398A9}" name="userId" dataDxfId="24">
+    <tableColumn id="6" xr3:uid="{0A7CDBA9-FD84-4CC8-8EDF-CD8D694398A9}" name="userId" dataDxfId="27">
       <calculatedColumnFormula>_xlfn.XLOOKUP(ParticipantTable[[#This Row],[userName]],UserTable[name],UserTable[id],"",0,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{F6E3050B-3F30-48C9-AAC7-FCAD98900424}" name="participantTypeId" dataDxfId="23">
+    <tableColumn id="7" xr3:uid="{F6E3050B-3F30-48C9-AAC7-FCAD98900424}" name="participantTypeId" dataDxfId="26">
       <calculatedColumnFormula>_xlfn.XLOOKUP(ParticipantTable[[#This Row],[participantTypeName]],ParticipantTypeTable[name],ParticipantTypeTable[id],"",0,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{DACCFE94-858F-47FE-B4F6-B33E5374D14F}" name="hours" dataDxfId="22"/>
-    <tableColumn id="9" xr3:uid="{896BC859-D635-4695-B906-023A1E5FE6E6}" name="startAt" dataDxfId="21"/>
-    <tableColumn id="10" xr3:uid="{DFC6A317-6999-46F4-8CCD-ACD83FFB9F5E}" name="endAt" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{DACCFE94-858F-47FE-B4F6-B33E5374D14F}" name="hours" dataDxfId="25"/>
+    <tableColumn id="9" xr3:uid="{896BC859-D635-4695-B906-023A1E5FE6E6}" name="startAt" dataDxfId="24"/>
+    <tableColumn id="10" xr3:uid="{DFC6A317-6999-46F4-8CCD-ACD83FFB9F5E}" name="endAt" dataDxfId="23"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{E4DFEBB4-E470-43F4-9B57-CA71A40CB7EA}" name="CertificateTable" displayName="CertificateTable" ref="A6:B13" totalsRowShown="0" headerRowDxfId="19" headerRowBorderDxfId="18" tableBorderDxfId="17" totalsRowBorderDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{E4DFEBB4-E470-43F4-9B57-CA71A40CB7EA}" name="CertificateTable" displayName="CertificateTable" ref="A6:B13" totalsRowShown="0" headerRowDxfId="22" headerRowBorderDxfId="21" tableBorderDxfId="20" totalsRowBorderDxfId="19">
   <autoFilter ref="A6:B13" xr:uid="{E4DFEBB4-E470-43F4-9B57-CA71A40CB7EA}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{61038C46-43E9-4B35-96C1-CBBB1A87E834}" name="id" dataDxfId="15">
+    <tableColumn id="1" xr3:uid="{61038C46-43E9-4B35-96C1-CBBB1A87E834}" name="id" dataDxfId="18">
       <calculatedColumnFormula>IF(ISBLANK(CertificateTable[[#This Row],[name]]),"",ROW()-6)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{33957B68-51D0-43D0-8BD3-562B4F9472E0}" name="name" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{33957B68-51D0-43D0-8BD3-562B4F9472E0}" name="name" dataDxfId="17"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6508,7 +6508,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="108" t="s">
+      <c r="A1" s="107" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="105"/>
@@ -6719,12 +6719,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="104" t="s">
         <v>222</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
       <c r="E1" s="105"/>
       <c r="F1" s="105"/>
       <c r="G1" s="105"/>
@@ -6733,12 +6733,12 @@
       <c r="J1" s="105"/>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="104" t="s">
+      <c r="A2" s="106" t="s">
         <v>223</v>
       </c>
-      <c r="B2" s="104"/>
-      <c r="C2" s="104"/>
-      <c r="D2" s="104"/>
+      <c r="B2" s="106"/>
+      <c r="C2" s="106"/>
+      <c r="D2" s="106"/>
       <c r="E2" s="105"/>
       <c r="F2" s="105"/>
       <c r="G2" s="105"/>
@@ -6939,13 +6939,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="104" t="s">
         <v>238</v>
       </c>
       <c r="B1" s="105"/>
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="104" t="s">
+      <c r="A2" s="106" t="s">
         <v>239</v>
       </c>
       <c r="B2" s="105"/>
@@ -7069,10 +7069,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="104" t="s">
         <v>245</v>
       </c>
-      <c r="B1" s="107"/>
+      <c r="B1" s="109"/>
       <c r="C1" s="105"/>
       <c r="D1" s="105"/>
       <c r="E1" s="105"/>
@@ -7082,10 +7082,10 @@
       <c r="I1" s="105"/>
     </row>
     <row r="2" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="104" t="s">
+      <c r="A2" s="106" t="s">
         <v>246</v>
       </c>
-      <c r="B2" s="104"/>
+      <c r="B2" s="106"/>
       <c r="C2" s="105"/>
       <c r="D2" s="105"/>
       <c r="E2" s="105"/>
@@ -7404,21 +7404,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="104" t="s">
         <v>257</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
+      <c r="B1" s="104"/>
+      <c r="C1" s="104"/>
       <c r="D1" s="105"/>
       <c r="E1" s="105"/>
       <c r="F1" s="105"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="104" t="s">
+      <c r="A2" s="106" t="s">
         <v>258</v>
       </c>
-      <c r="B2" s="104"/>
-      <c r="C2" s="104"/>
+      <c r="B2" s="106"/>
+      <c r="C2" s="106"/>
       <c r="D2" s="105"/>
       <c r="E2" s="105"/>
       <c r="F2" s="105"/>
@@ -7565,7 +7565,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="104" t="s">
         <v>265</v>
       </c>
       <c r="B1" s="105"/>
@@ -7576,7 +7576,7 @@
       <c r="G1" s="105"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="104" t="s">
+      <c r="A2" s="106" t="s">
         <v>266</v>
       </c>
       <c r="B2" s="105"/>
@@ -7765,7 +7765,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="109" t="s">
+      <c r="A1" s="108" t="s">
         <v>36</v>
       </c>
       <c r="B1" s="105"/>
@@ -7849,13 +7849,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="109" t="s">
         <v>52</v>
       </c>
       <c r="B1" s="105"/>
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="104" t="s">
+      <c r="A2" s="106" t="s">
         <v>53</v>
       </c>
       <c r="B2" s="105"/>
@@ -7939,7 +7939,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="109" t="s">
         <v>63</v>
       </c>
       <c r="B1" s="105"/>
@@ -7948,7 +7948,7 @@
       <c r="E1" s="105"/>
     </row>
     <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="104" t="s">
+      <c r="A2" s="106" t="s">
         <v>64</v>
       </c>
       <c r="B2" s="105"/>
@@ -8176,22 +8176,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="104" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="106"/>
-      <c r="C1" s="106"/>
-      <c r="D1" s="106"/>
-      <c r="E1" s="106"/>
-      <c r="F1" s="106"/>
-      <c r="G1" s="106"/>
-      <c r="H1" s="106"/>
-      <c r="I1" s="106"/>
-      <c r="J1" s="106"/>
-      <c r="K1" s="106"/>
-      <c r="L1" s="106"/>
-      <c r="M1" s="106"/>
-      <c r="N1" s="106"/>
+      <c r="B1" s="104"/>
+      <c r="C1" s="104"/>
+      <c r="D1" s="104"/>
+      <c r="E1" s="104"/>
+      <c r="F1" s="104"/>
+      <c r="G1" s="104"/>
+      <c r="H1" s="104"/>
+      <c r="I1" s="104"/>
+      <c r="J1" s="104"/>
+      <c r="K1" s="104"/>
+      <c r="L1" s="104"/>
+      <c r="M1" s="104"/>
+      <c r="N1" s="104"/>
     </row>
     <row r="2" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="110" t="s">
@@ -9417,7 +9417,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="104" t="s">
         <v>158</v>
       </c>
       <c r="B1" s="105"/>
@@ -9427,7 +9427,7 @@
       <c r="F1" s="105"/>
     </row>
     <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="104" t="s">
+      <c r="A2" s="106" t="s">
         <v>159</v>
       </c>
       <c r="B2" s="105"/>
@@ -10068,13 +10068,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="104" t="s">
         <v>176</v>
       </c>
       <c r="B1" s="105"/>
     </row>
     <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="104" t="s">
+      <c r="A2" s="106" t="s">
         <v>177</v>
       </c>
       <c r="B2" s="105"/>
@@ -10195,10 +10195,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="104" t="s">
         <v>186</v>
       </c>
-      <c r="B1" s="107"/>
+      <c r="B1" s="109"/>
       <c r="C1" s="105"/>
       <c r="D1" s="105"/>
       <c r="E1" s="105"/>
@@ -10207,10 +10207,10 @@
       <c r="H1" s="105"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="104" t="s">
+      <c r="A2" s="106" t="s">
         <v>187</v>
       </c>
-      <c r="B2" s="104"/>
+      <c r="B2" s="106"/>
       <c r="C2" s="105"/>
       <c r="D2" s="105"/>
       <c r="E2" s="105"/>
@@ -10411,7 +10411,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="104" t="s">
         <v>207</v>
       </c>
       <c r="B1" s="105"/>
@@ -10422,7 +10422,7 @@
       <c r="G1" s="105"/>
     </row>
     <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="104" t="s">
+      <c r="A2" s="106" t="s">
         <v>208</v>
       </c>
       <c r="B2" s="105"/>

--- a/prisma/data/estructura_bd.xlsx
+++ b/prisma/data/estructura_bd.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tomas\Documents\proyectos\constancias-doctorado\prisma\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBE2063F-B5B5-4E52-96AB-65765A2444E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C368AD34-0134-4530-8EF4-6143E93833CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="📌 Índice" sheetId="1" r:id="rId1"/>
@@ -99,7 +99,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="786" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="474">
   <si>
     <t>📌 Índice de Tablas</t>
   </si>
@@ -1410,9 +1410,6 @@
   </si>
   <si>
     <t>4908a18d-bbc2-42bf-9374-f4b4874eedc0</t>
-  </si>
-  <si>
-    <t>22.376.316-2</t>
   </si>
   <si>
     <t>Super Administrador</t>
@@ -1459,6 +1456,87 @@
     </r>
   </si>
   <si>
+    <t>{director.academicDegree.title[0].abbrev director.name}, {director.gender==MALE?Director:Directora} del Programa de Doctorado en Ciencias Médicas, de la Universidad de La Frontera, deja constancia que {user.name}, participó como Tutor de Tesis y Evaluador interno en el examen de grado del Estudiante, llevada a cabo el {activity.startAt}, Tesis Titulada “{activity.name}” </t>
+  </si>
+  <si>
+    <t>{director.academicDegree.title[0].abbrev director.name}, {director.gender==MALE?Director:Directora} del Programa de Doctorado en Ciencias Médicas, de la Universidad de La Frontera, deja constancia que {user.name}, matrícula Nº {user.student.studentId}, RUT {user.rut}, es {user.gender==MALE?alumno:alumna} regular de nuestro programa y que con fecha {activity.startAt}, aprobó su examen de calificación con nota: {user.exam[0].grade}</t>
+  </si>
+  <si>
+    <t>Louise Zanella Martins</t>
+  </si>
+  <si>
+    <t>Rodrigo Rivera Concha</t>
+  </si>
+  <si>
+    <t>Javier Hernan Alarcon Roa</t>
+  </si>
+  <si>
+    <t>Lorena Carlota Albarracin Navas</t>
+  </si>
+  <si>
+    <t>Javier Ignacio Arriagada Gacitúa</t>
+  </si>
+  <si>
+    <t>Sandra Paulina Catalan Monsalve</t>
+  </si>
+  <si>
+    <t>Hugo Alfredo Delgado Muñoz</t>
+  </si>
+  <si>
+    <t>Galo Ruben Duque Proaño</t>
+  </si>
+  <si>
+    <t>Maria Elena Espinosa Gonzalez</t>
+  </si>
+  <si>
+    <t>Mirta Andrea Espinoza Cid</t>
+  </si>
+  <si>
+    <t>Maria Fernanda Garcia Aguilera</t>
+  </si>
+  <si>
+    <t>Álvaro Ignacio Godoy Díaz</t>
+  </si>
+  <si>
+    <t>Enmanuel Isidoro Guerrero Quiroz</t>
+  </si>
+  <si>
+    <t>Juan Pablo Holguin Carvajal</t>
+  </si>
+  <si>
+    <t>Mariela Alejandra Landero Fuentes</t>
+  </si>
+  <si>
+    <t>Nicolás Ignacio Lara Salas</t>
+  </si>
+  <si>
+    <t>Pamela Constanza Lavados Romo</t>
+  </si>
+  <si>
+    <t>Miriann Alexandra Mora Verdugo</t>
+  </si>
+  <si>
+    <t>Eudoxia Georgina Muñoz Ortiz</t>
+  </si>
+  <si>
+    <t>Orieta Del Pilar Navarrete Fernandez</t>
+  </si>
+  <si>
+    <t>Guissela Romane Quiroz Sievers</t>
+  </si>
+  <si>
+    <t>Josue David Rivadeneira Dueñas</t>
+  </si>
+  <si>
+    <t>Carla Marina Salgado Castillo</t>
+  </si>
+  <si>
+    <t>Sergio Antonio Sotelo Hernandez</t>
+  </si>
+  <si>
+    <t>Paulina Antonia Vasquez Aguilar</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">{director.academicDegree.title[0].abbrev director.name}, {director.gender==MALE?Director:Directora} del </t>
     </r>
@@ -1477,14 +1555,15 @@
         <color rgb="FF000000"/>
         <rFont val="Trebuchet MS"/>
       </rPr>
-      <t xml:space="preserve"> de la Universidad de La Frontera, deja constancia que {user.name}, {user.rut}, ha impartido docencia para los alumnos del programa de acuerdo al siguiente detalle: Detalle Actividad</t>
+      <t xml:space="preserve"> de la Universidad de La Frontera, deja constancia que {user.name}, {user.rut}, ha impartido docencia para los alumnos del programa de acuerdo al siguiente detalle:
+  -     Durante {activity.name} con el rol de {user.participants[0].participantType.name} un total de {user.participants[0].hours} horas en el semestre {user.participants[0].startAt} </t>
     </r>
   </si>
   <si>
-    <t>{director.academicDegree.title[0].abbrev director.name}, {director.gender==MALE?Director:Directora} del Programa de Doctorado en Ciencias Médicas, de la Universidad de La Frontera, deja constancia que {user.name}, participó como Tutor de Tesis y Evaluador interno en el examen de grado del Estudiante, llevada a cabo el {activity.startAt}, Tesis Titulada “{activity.name}” </t>
-  </si>
-  <si>
-    <t>{director.academicDegree.title[0].abbrev director.name}, {director.gender==MALE?Director:Directora} del Programa de Doctorado en Ciencias Médicas, de la Universidad de La Frontera, deja constancia que {user.name}, matrícula Nº {user.student.studentId}, RUT {user.rut}, es {user.gender==MALE?alumno:alumna} regular de nuestro programa y que con fecha {activity.startAt}, aprobó su examen de calificación con nota: {user.exam[0].grade}</t>
+    <t>8db366bd-48a8-4a70-bb6f-ed3e26e846ae</t>
+  </si>
+  <si>
+    <t>Solicitud Especial</t>
   </si>
 </sst>
 </file>
@@ -1778,7 +1857,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -2004,12 +2083,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFAAAAAA"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFAAAAAA"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFAAAAAA"/>
+      </top>
+      <bottom style="thin">
+        <color theme="6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="115">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2358,6 +2452,18 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="12" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="14" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2421,6 +2527,330 @@
           <bgColor rgb="FFFFFFFF"/>
         </patternFill>
       </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF0FFF4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -2850,6 +3280,321 @@
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="164" formatCode="dd/mm/yy;@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="dd/mm/yy;@"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -2936,6 +3681,936 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF0FFF4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF0FFF4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF0FFF4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF0FFF4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF0FFF4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <border outline="0">
         <bottom style="thin">
           <color rgb="FFAAAAAA"/>
@@ -3031,15 +4706,14 @@
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="164" formatCode="dd/mm/yy;@"/>
       <fill>
         <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor indexed="64"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FFAAAAAA"/>
         </left>
@@ -3053,6 +4727,11 @@
           <color rgb="FFAAAAAA"/>
         </bottom>
       </border>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
     </dxf>
     <dxf>
       <font>
@@ -3070,7 +4749,7 @@
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
+      <numFmt numFmtId="0" formatCode="General"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -3078,7 +4757,7 @@
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color rgb="FFAAAAAA"/>
         </left>
@@ -3091,44 +4770,8 @@
         <bottom style="thin">
           <color rgb="FFAAAAAA"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -3187,6 +4830,7 @@
         <name val="Arial"/>
         <scheme val="none"/>
       </font>
+      <numFmt numFmtId="30" formatCode="@"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -3194,7 +4838,7 @@
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FFAAAAAA"/>
         </left>
@@ -3207,128 +4851,6 @@
         <bottom style="thin">
           <color rgb="FFAAAAAA"/>
         </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -3479,12 +5001,137 @@
           <bgColor rgb="FFF0FFF4"/>
         </patternFill>
       </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+      </border>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color rgb="FFAAAAAA"/>
         </left>
-        <right/>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
         <top style="thin">
           <color rgb="FFAAAAAA"/>
         </top>
@@ -3522,7 +5169,9 @@
         <left style="thin">
           <color rgb="FFAAAAAA"/>
         </left>
-        <right/>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
         <top style="thin">
           <color rgb="FFAAAAAA"/>
         </top>
@@ -3627,8 +5276,93 @@
         <sz val="10"/>
         <color auto="1"/>
         <name val="Arial"/>
+        <family val="2"/>
         <scheme val="none"/>
       </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF0FFF4"/>
+          <bgColor indexed="64"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+      </border>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="30" formatCode="@"/>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -3733,25 +5467,9 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color rgb="FFAAAAAA"/>
         </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -3777,13 +5495,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -3911,132 +5622,13 @@
         <sz val="10"/>
         <color auto="1"/>
         <name val="Arial"/>
+        <family val="2"/>
         <scheme val="none"/>
       </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFF0FFF4"/>
         </patternFill>
       </fill>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -4159,30 +5751,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <border outline="0">
         <bottom style="thin">
           <color rgb="FFAAAAAA"/>
@@ -4251,6 +5819,110 @@
           <color rgb="FFAAAAAA"/>
         </left>
         <right/>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFAAAAAA"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FFAAAAAA"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFF0FFF4"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFAAAAAA"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFAAAAAA"/>
+        </right>
         <top style="thin">
           <color rgb="FFAAAAAA"/>
         </top>
@@ -4321,1571 +5993,6 @@
           <color rgb="FFAAAAAA"/>
         </bottom>
       </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF0FFF4"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="dd/mm/yy;@"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor indexed="64"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-      </border>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="30" formatCode="@"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF0FFF4"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF0FFF4"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-      </border>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF0FFF4"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF0FFF4"/>
-          <bgColor indexed="64"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-      </border>
-      <extLst>
-        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
-          <xfpb:DXFComplement i="0"/>
-        </ext>
-      </extLst>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF0FFF4"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF0FFF4"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF0FFF4"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFF0FFF4"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color rgb="FFAAAAAA"/>
-        </left>
-        <right style="thin">
-          <color rgb="FFAAAAAA"/>
-        </right>
-        <top style="thin">
-          <color rgb="FFAAAAAA"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FFAAAAAA"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border outline="0">
@@ -5971,58 +6078,58 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{21BDF646-6AB5-43B7-AD3B-7DFA6765727B}" name="ADegreeTable" displayName="ADegreeTable" ref="A6:B8" totalsRowShown="0" headerRowDxfId="108" headerRowBorderDxfId="107" tableBorderDxfId="106" totalsRowBorderDxfId="105">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{21BDF646-6AB5-43B7-AD3B-7DFA6765727B}" name="ADegreeTable" displayName="ADegreeTable" ref="A6:B8" totalsRowShown="0" headerRowDxfId="113" headerRowBorderDxfId="112" tableBorderDxfId="111" totalsRowBorderDxfId="110">
   <autoFilter ref="A6:B8" xr:uid="{21BDF646-6AB5-43B7-AD3B-7DFA6765727B}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{D084344C-E421-48F0-8ED9-9638F88C6846}" name="id"/>
-    <tableColumn id="2" xr3:uid="{9F0DCB94-4F04-48E3-B0C1-197AD7B74B6B}" name="name" dataDxfId="104"/>
+    <tableColumn id="2" xr3:uid="{9F0DCB94-4F04-48E3-B0C1-197AD7B74B6B}" name="name" dataDxfId="109"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{7B666A61-9D82-4C49-BCCD-2E916244936B}" name="TemplateTable" displayName="TemplateTable" ref="A6:I11" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13" totalsRowBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{7B666A61-9D82-4C49-BCCD-2E916244936B}" name="TemplateTable" displayName="TemplateTable" ref="A6:I11" totalsRowShown="0" headerRowDxfId="27" dataDxfId="25" headerRowBorderDxfId="26" tableBorderDxfId="24" totalsRowBorderDxfId="23">
   <autoFilter ref="A6:I11" xr:uid="{7B666A61-9D82-4C49-BCCD-2E916244936B}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{35DFD295-E223-4974-ACE2-697935223713}" name="id" dataDxfId="11">
+    <tableColumn id="1" xr3:uid="{35DFD295-E223-4974-ACE2-697935223713}" name="id" dataDxfId="22">
       <calculatedColumnFormula>IF(ISBLANK(TemplateTable[[#This Row],[certificateName]]),"",ROW()-6)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{F0014E9D-997A-4846-891A-BB433D709D81}" name="certificateName" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{6800626F-D286-415C-A674-0DB3C1DB73C2}" name="certificateId" dataDxfId="9">
+    <tableColumn id="2" xr3:uid="{F0014E9D-997A-4846-891A-BB433D709D81}" name="certificateName" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{6800626F-D286-415C-A674-0DB3C1DB73C2}" name="certificateId" dataDxfId="20">
       <calculatedColumnFormula>_xlfn.XLOOKUP(TemplateTable[[#This Row],[certificateName]],CertificateTable[name], CertificateTable[id],"",0,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{98120E82-B208-4584-AA36-331D4263F344}" name="role" dataDxfId="8"/>
-    <tableColumn id="8" xr3:uid="{1EC5D45E-1355-4169-9B29-F2DD20E04EC2}" name="activityTypeName" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{BFE3FA6C-D650-450B-9013-3E601CEFEAB9}" name="activityTypeId" dataDxfId="6">
+    <tableColumn id="4" xr3:uid="{98120E82-B208-4584-AA36-331D4263F344}" name="role" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{1EC5D45E-1355-4169-9B29-F2DD20E04EC2}" name="activityTypeName" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{BFE3FA6C-D650-450B-9013-3E601CEFEAB9}" name="activityTypeId" dataDxfId="17">
       <calculatedColumnFormula>_xlfn.XLOOKUP(TemplateTable[[#This Row],[activityTypeName]], ActivityTypeTable[name],ActivityTypeTable[id], "",0,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{D2A34400-809B-4181-B7DE-643FA4E237AC}" name="participantTypeName" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{C114DF71-6DF2-480D-932F-564F087EDE4D}" name="participantTypeId" dataDxfId="4">
+    <tableColumn id="9" xr3:uid="{D2A34400-809B-4181-B7DE-643FA4E237AC}" name="participantTypeName" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{C114DF71-6DF2-480D-932F-564F087EDE4D}" name="participantTypeId" dataDxfId="15">
       <calculatedColumnFormula>_xlfn.XLOOKUP(TemplateTable[[#This Row],[participantTypeName]], ParticipantTypeTable[name], ParticipantTypeTable[id],"",0,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{718F385C-1FA2-47C7-A2A8-851AF99822CD}" name="template" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{718F385C-1FA2-47C7-A2A8-851AF99822CD}" name="template" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BC5C6D74-FC52-47E2-AA34-D6697409B949}" name="ExamTable" displayName="ExamTable" ref="A6:F7" totalsRowShown="0" headerRowDxfId="119" dataDxfId="117" headerRowBorderDxfId="118" tableBorderDxfId="116" totalsRowBorderDxfId="115">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BC5C6D74-FC52-47E2-AA34-D6697409B949}" name="ExamTable" displayName="ExamTable" ref="A6:F7" totalsRowShown="0" headerRowDxfId="13" dataDxfId="11" headerRowBorderDxfId="12" tableBorderDxfId="10" totalsRowBorderDxfId="9">
   <autoFilter ref="A6:F7" xr:uid="{BC5C6D74-FC52-47E2-AA34-D6697409B949}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{692719ED-79B2-42F7-9EE5-149A32F745B3}" name="id" dataDxfId="114">
+    <tableColumn id="1" xr3:uid="{692719ED-79B2-42F7-9EE5-149A32F745B3}" name="id" dataDxfId="8">
       <calculatedColumnFormula>IF(ISBLANK(ExamTable[[#This Row],[studentName]]),"",ROW()-6)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{1B246D39-0161-43B5-A25E-5F63C4AE1C13}" name="studentName" dataDxfId="113"/>
-    <tableColumn id="3" xr3:uid="{9CA5A4E7-4070-4BCC-8ABE-22A888226F06}" name="activityName" dataDxfId="112"/>
-    <tableColumn id="4" xr3:uid="{21CCAFCC-797A-43FF-B871-B5CE4FD3B169}" name="studentId" dataDxfId="111">
+    <tableColumn id="2" xr3:uid="{1B246D39-0161-43B5-A25E-5F63C4AE1C13}" name="studentName" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{9CA5A4E7-4070-4BCC-8ABE-22A888226F06}" name="activityName" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{21CCAFCC-797A-43FF-B871-B5CE4FD3B169}" name="studentId" dataDxfId="5">
       <calculatedColumnFormula>_xlfn.XLOOKUP(ExamTable[[#This Row],[studentName]],StudentTable[userName],StudentTable[id],"",0,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{6E4D44FF-C970-45A8-9C7A-5AE471194553}" name="activityId" dataDxfId="110">
+    <tableColumn id="5" xr3:uid="{6E4D44FF-C970-45A8-9C7A-5AE471194553}" name="activityId" dataDxfId="4">
       <calculatedColumnFormula>_xlfn.XLOOKUP(ExamTable[[#This Row],[activityName]],ActivityTable[name], ActivityTable[id],"",0,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{9C8DA54A-7DAD-473A-A016-641BD60DCBEA}" name="grade" dataDxfId="109"/>
+    <tableColumn id="6" xr3:uid="{9C8DA54A-7DAD-473A-A016-641BD60DCBEA}" name="grade" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6048,41 +6155,41 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{1D06504D-941D-4F95-A34D-8031062A23F0}" name="TitleTable" displayName="TitleTable" ref="A6:E12" totalsRowShown="0" headerRowDxfId="103" headerRowBorderDxfId="102" tableBorderDxfId="101" totalsRowBorderDxfId="100">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{1D06504D-941D-4F95-A34D-8031062A23F0}" name="TitleTable" displayName="TitleTable" ref="A6:E12" totalsRowShown="0" headerRowDxfId="108" headerRowBorderDxfId="107" tableBorderDxfId="106" totalsRowBorderDxfId="105">
   <autoFilter ref="A6:E12" xr:uid="{1D06504D-941D-4F95-A34D-8031062A23F0}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{7801D28A-9FC1-4168-B38F-EE639910650A}" name="id" dataDxfId="99">
+    <tableColumn id="1" xr3:uid="{7801D28A-9FC1-4168-B38F-EE639910650A}" name="id" dataDxfId="104">
       <calculatedColumnFormula>IF(TitleTable[[#This Row],[academicDegreeId]]&lt;&gt;"",ROW()-6,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{A7BC7DF6-3102-4BBA-BC51-DB8410EAB5BD}" name="academicDegreeId" dataDxfId="98">
+    <tableColumn id="2" xr3:uid="{A7BC7DF6-3102-4BBA-BC51-DB8410EAB5BD}" name="academicDegreeId" dataDxfId="103">
       <calculatedColumnFormula>_xlfn.XLOOKUP(TitleTable[[#This Row],[AcademicDegreeName]],ADegreeTable[name], ADegreeTable[id],"",0,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{A4F7459D-7F69-4F60-BB9E-B23C34251DCF}" name="AcademicDegreeName" dataDxfId="97"/>
-    <tableColumn id="3" xr3:uid="{300E313B-FA95-4376-9612-7FF1A398FA49}" name="gender" dataDxfId="96"/>
-    <tableColumn id="4" xr3:uid="{30F0397B-1916-4C7E-B449-91C6BCF48ADA}" name="abbrev" dataDxfId="95"/>
+    <tableColumn id="6" xr3:uid="{A4F7459D-7F69-4F60-BB9E-B23C34251DCF}" name="AcademicDegreeName" dataDxfId="102"/>
+    <tableColumn id="3" xr3:uid="{300E313B-FA95-4376-9612-7FF1A398FA49}" name="gender" dataDxfId="101"/>
+    <tableColumn id="4" xr3:uid="{30F0397B-1916-4C7E-B449-91C6BCF48ADA}" name="abbrev" dataDxfId="100"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{85FEA289-536E-4259-A619-2744ADA3DB87}" name="UserTable" displayName="UserTable" ref="A6:N36" totalsRowShown="0" headerRowDxfId="94" dataDxfId="93" tableBorderDxfId="92">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{85FEA289-536E-4259-A619-2744ADA3DB87}" name="UserTable" displayName="UserTable" ref="A6:N36" totalsRowShown="0" headerRowDxfId="99" dataDxfId="98" tableBorderDxfId="97">
   <autoFilter ref="A6:N36" xr:uid="{85FEA289-536E-4259-A619-2744ADA3DB87}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{D84565A3-15A3-40D5-885B-59C4991B2454}" name="id" dataDxfId="91">
+    <tableColumn id="1" xr3:uid="{D84565A3-15A3-40D5-885B-59C4991B2454}" name="id" dataDxfId="96">
       <calculatedColumnFormula>IF(UserTable[[#This Row],[rut]]&lt;&gt;"", ROW()-6,"")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{E789B167-226C-420B-BBD4-8755387CAFE6}" name="rut" dataDxfId="90"/>
-    <tableColumn id="3" xr3:uid="{93B4A9A1-DC9A-44FA-8692-C9A24CC1BF40}" name="name" dataDxfId="89"/>
-    <tableColumn id="4" xr3:uid="{63AB093F-B349-4655-86C2-B260E78F6BF1}" name="email" dataDxfId="88"/>
-    <tableColumn id="5" xr3:uid="{56D0A7C0-F001-4955-A153-E7F45CC5AF52}" name="emailVerified" dataDxfId="87"/>
-    <tableColumn id="6" xr3:uid="{7D04D1EC-A119-48D6-AD1F-240337054887}" name="image" dataDxfId="86"/>
-    <tableColumn id="7" xr3:uid="{CF3A91BB-659C-4083-935E-AFC637FBA3F3}" name="role" dataDxfId="85"/>
-    <tableColumn id="8" xr3:uid="{5C06DE85-13EF-4A5C-B6DB-B75E5FFC0545}" name="banned" dataDxfId="84"/>
-    <tableColumn id="9" xr3:uid="{8BFEF23D-7870-4777-A520-8246B3DE2FDF}" name="banReason" dataDxfId="83"/>
-    <tableColumn id="10" xr3:uid="{F672B4C8-D389-49C1-9B64-DE4E88445A59}" name="banExpires" dataDxfId="82"/>
-    <tableColumn id="11" xr3:uid="{90307C6C-1290-4627-8E69-FF7293A360C8}" name="gender" dataDxfId="81"/>
-    <tableColumn id="12" xr3:uid="{AFFA8672-1495-4235-9B93-04970AC93F2A}" name="isDirector" dataDxfId="80"/>
+    <tableColumn id="2" xr3:uid="{E789B167-226C-420B-BBD4-8755387CAFE6}" name="rut" dataDxfId="95"/>
+    <tableColumn id="3" xr3:uid="{93B4A9A1-DC9A-44FA-8692-C9A24CC1BF40}" name="name" dataDxfId="94"/>
+    <tableColumn id="4" xr3:uid="{63AB093F-B349-4655-86C2-B260E78F6BF1}" name="email" dataDxfId="93"/>
+    <tableColumn id="5" xr3:uid="{56D0A7C0-F001-4955-A153-E7F45CC5AF52}" name="emailVerified" dataDxfId="92"/>
+    <tableColumn id="6" xr3:uid="{7D04D1EC-A119-48D6-AD1F-240337054887}" name="image" dataDxfId="91"/>
+    <tableColumn id="7" xr3:uid="{CF3A91BB-659C-4083-935E-AFC637FBA3F3}" name="role" dataDxfId="90"/>
+    <tableColumn id="8" xr3:uid="{5C06DE85-13EF-4A5C-B6DB-B75E5FFC0545}" name="banned" dataDxfId="89"/>
+    <tableColumn id="9" xr3:uid="{8BFEF23D-7870-4777-A520-8246B3DE2FDF}" name="banReason" dataDxfId="88"/>
+    <tableColumn id="10" xr3:uid="{F672B4C8-D389-49C1-9B64-DE4E88445A59}" name="banExpires" dataDxfId="87"/>
+    <tableColumn id="11" xr3:uid="{90307C6C-1290-4627-8E69-FF7293A360C8}" name="gender" dataDxfId="86"/>
+    <tableColumn id="12" xr3:uid="{AFFA8672-1495-4235-9B93-04970AC93F2A}" name="isDirector" dataDxfId="85"/>
     <tableColumn id="13" xr3:uid="{623D3833-0700-46BB-9F79-F1EBAFC81D6A}" name="academicDegreeId">
       <calculatedColumnFormula>_xlfn.XLOOKUP(UserTable[[#This Row],[academicDegreeName]], ADegreeTable[name], ADegreeTable[id],"",0,1)</calculatedColumnFormula>
     </tableColumn>
@@ -6093,111 +6200,111 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{FCF25C97-1CFC-458F-A99C-18D9A6AD8A69}" name="StudentTable" displayName="StudentTable" ref="A6:F31" totalsRowShown="0" headerRowDxfId="79" dataDxfId="77" headerRowBorderDxfId="78" tableBorderDxfId="76" totalsRowBorderDxfId="75">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{FCF25C97-1CFC-458F-A99C-18D9A6AD8A69}" name="StudentTable" displayName="StudentTable" ref="A6:F31" totalsRowShown="0" headerRowDxfId="84" dataDxfId="82" headerRowBorderDxfId="83" tableBorderDxfId="81" totalsRowBorderDxfId="80">
   <autoFilter ref="A6:F31" xr:uid="{FCF25C97-1CFC-458F-A99C-18D9A6AD8A69}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{4365B9E5-05D3-43F2-9E75-34DB73C72A3F}" name="id" dataDxfId="74">
+    <tableColumn id="1" xr3:uid="{4365B9E5-05D3-43F2-9E75-34DB73C72A3F}" name="id" dataDxfId="79">
       <calculatedColumnFormula>IF(ISBLANK(StudentTable[[#This Row],[studentId]]),"", ROW()-6)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{EAC8744D-1F09-4A5C-8E4A-3D85E08B6D37}" name="studentId" dataDxfId="73"/>
-    <tableColumn id="3" xr3:uid="{66B37519-AF27-4C0F-9BFE-4DE89E499C64}" name="userName" dataDxfId="72"/>
-    <tableColumn id="4" xr3:uid="{76391975-9083-4AF9-B31F-55AE28819CFB}" name="userId" dataDxfId="71">
+    <tableColumn id="2" xr3:uid="{EAC8744D-1F09-4A5C-8E4A-3D85E08B6D37}" name="studentId" dataDxfId="78"/>
+    <tableColumn id="3" xr3:uid="{66B37519-AF27-4C0F-9BFE-4DE89E499C64}" name="userName" dataDxfId="77"/>
+    <tableColumn id="4" xr3:uid="{76391975-9083-4AF9-B31F-55AE28819CFB}" name="userId" dataDxfId="76">
       <calculatedColumnFormula>_xlfn.XLOOKUP(StudentTable[[#This Row],[userName]],UserTable[name],UserTable[id],"",0,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{BD538411-70FF-493E-B572-8105AB255D28}" name="isRegularStudent" dataDxfId="70"/>
-    <tableColumn id="6" xr3:uid="{D2EBA512-F8A8-4CB6-8EA2-A0DC38CB5C0B}" name="admisionDate" dataDxfId="69"/>
+    <tableColumn id="5" xr3:uid="{BD538411-70FF-493E-B572-8105AB255D28}" name="isRegularStudent" dataDxfId="75"/>
+    <tableColumn id="6" xr3:uid="{D2EBA512-F8A8-4CB6-8EA2-A0DC38CB5C0B}" name="admisionDate" dataDxfId="74"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{0F547C4C-61C7-4C2A-9C4D-C8523461AAFF}" name="ActivityTypeTable" displayName="ActivityTypeTable" ref="A6:B13" totalsRowShown="0" headerRowDxfId="68" headerRowBorderDxfId="67" tableBorderDxfId="66" totalsRowBorderDxfId="65">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{0F547C4C-61C7-4C2A-9C4D-C8523461AAFF}" name="ActivityTypeTable" displayName="ActivityTypeTable" ref="A6:B13" totalsRowShown="0" headerRowDxfId="73" headerRowBorderDxfId="72" tableBorderDxfId="71" totalsRowBorderDxfId="70">
   <autoFilter ref="A6:B13" xr:uid="{0F547C4C-61C7-4C2A-9C4D-C8523461AAFF}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{59150BA5-A7DE-4874-BEC8-662316686ECE}" name="id" dataDxfId="64">
+    <tableColumn id="1" xr3:uid="{59150BA5-A7DE-4874-BEC8-662316686ECE}" name="id" dataDxfId="69">
       <calculatedColumnFormula>IF(ISBLANK(ActivityTypeTable[[#This Row],[name]]),"", ROW()-6)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{C734BFB6-8090-4FE5-B857-573748EB0614}" name="name" dataDxfId="63"/>
+    <tableColumn id="2" xr3:uid="{C734BFB6-8090-4FE5-B857-573748EB0614}" name="name" dataDxfId="68"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{DF67C1A1-6942-4B9F-AE16-A9B361C53B1A}" name="ActivityTable" displayName="ActivityTable" ref="A6:H7" totalsRowShown="0" headerRowDxfId="62" dataDxfId="60" headerRowBorderDxfId="61" tableBorderDxfId="59" totalsRowBorderDxfId="58">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{DF67C1A1-6942-4B9F-AE16-A9B361C53B1A}" name="ActivityTable" displayName="ActivityTable" ref="A6:H7" totalsRowShown="0" headerRowDxfId="67" dataDxfId="65" headerRowBorderDxfId="66" tableBorderDxfId="64" totalsRowBorderDxfId="63">
   <autoFilter ref="A6:H7" xr:uid="{DF67C1A1-6942-4B9F-AE16-A9B361C53B1A}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{ED578E86-4E76-4E90-85CA-674930C235F7}" name="id" dataDxfId="57"/>
-    <tableColumn id="2" xr3:uid="{FB6C5FA6-DF04-45A7-89B5-88F1FC79C2D6}" name="activityTypeName" dataDxfId="56"/>
-    <tableColumn id="3" xr3:uid="{EE938535-FAD5-46E2-9062-D0D81D92843E}" name="activityTypeId" dataDxfId="55">
+    <tableColumn id="1" xr3:uid="{ED578E86-4E76-4E90-85CA-674930C235F7}" name="id" dataDxfId="62"/>
+    <tableColumn id="2" xr3:uid="{FB6C5FA6-DF04-45A7-89B5-88F1FC79C2D6}" name="activityTypeName" dataDxfId="61"/>
+    <tableColumn id="3" xr3:uid="{EE938535-FAD5-46E2-9062-D0D81D92843E}" name="activityTypeId" dataDxfId="60">
       <calculatedColumnFormula>_xlfn.XLOOKUP(ActivityTable[[#This Row],[activityTypeName]],ActivityTypeTable[name], ActivityTypeTable[id],"",0,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{7E99DBF1-B701-4269-8285-40CB77EE77CF}" name="name" dataDxfId="54"/>
-    <tableColumn id="5" xr3:uid="{3F2225E0-5303-4D1E-95EC-65F1B96512C6}" name="startAt" dataDxfId="53"/>
-    <tableColumn id="6" xr3:uid="{D19CBEFD-D71A-41F7-A14B-DF9F5A8E0CA5}" name="endAt" dataDxfId="52"/>
-    <tableColumn id="7" xr3:uid="{A77D4338-9AE4-4919-BC5C-02F7DEF383DE}" name="nAssistant" dataDxfId="51"/>
-    <tableColumn id="8" xr3:uid="{AB81B6E6-2917-4082-9767-BA28157B6C97}" name="nParticipant" dataDxfId="50"/>
+    <tableColumn id="4" xr3:uid="{7E99DBF1-B701-4269-8285-40CB77EE77CF}" name="name" dataDxfId="59"/>
+    <tableColumn id="5" xr3:uid="{3F2225E0-5303-4D1E-95EC-65F1B96512C6}" name="startAt" dataDxfId="58"/>
+    <tableColumn id="6" xr3:uid="{D19CBEFD-D71A-41F7-A14B-DF9F5A8E0CA5}" name="endAt" dataDxfId="57"/>
+    <tableColumn id="7" xr3:uid="{A77D4338-9AE4-4919-BC5C-02F7DEF383DE}" name="nAssistant" dataDxfId="56"/>
+    <tableColumn id="8" xr3:uid="{AB81B6E6-2917-4082-9767-BA28157B6C97}" name="nParticipant" dataDxfId="55"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{23ADF508-CC90-4FBB-B8A6-80FFBB135690}" name="ParticipantTypeTable" displayName="ParticipantTypeTable" ref="A6:G22" totalsRowShown="0" headerRowDxfId="49" dataDxfId="47" headerRowBorderDxfId="48" tableBorderDxfId="46" totalsRowBorderDxfId="45">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{23ADF508-CC90-4FBB-B8A6-80FFBB135690}" name="ParticipantTypeTable" displayName="ParticipantTypeTable" ref="A6:G22" totalsRowShown="0" headerRowDxfId="54" dataDxfId="52" headerRowBorderDxfId="53" tableBorderDxfId="51" totalsRowBorderDxfId="50">
   <autoFilter ref="A6:G22" xr:uid="{23ADF508-CC90-4FBB-B8A6-80FFBB135690}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{10A749B4-38CA-4B67-A4C5-C561F90DDDE2}" name="id" dataDxfId="44">
+    <tableColumn id="1" xr3:uid="{10A749B4-38CA-4B67-A4C5-C561F90DDDE2}" name="id" dataDxfId="49">
       <calculatedColumnFormula>IF(ISBLANK(ParticipantTypeTable[[#This Row],[name]]),"", ROW()-6)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{04AFB6EC-E691-421A-B26F-9891A42D291E}" name="name" dataDxfId="43"/>
-    <tableColumn id="3" xr3:uid="{12DF8505-E053-492C-8C45-4D52788AA007}" name="roles" dataDxfId="42"/>
-    <tableColumn id="4" xr3:uid="{D684A6E0-2CB6-43AD-AA2A-978621E5D4DB}" name="activityTypeName" dataDxfId="41"/>
-    <tableColumn id="5" xr3:uid="{8BB7BDF5-9C51-428B-8F41-2D5551800DA8}" name="activityTypeId" dataDxfId="40">
+    <tableColumn id="2" xr3:uid="{04AFB6EC-E691-421A-B26F-9891A42D291E}" name="name" dataDxfId="48"/>
+    <tableColumn id="3" xr3:uid="{12DF8505-E053-492C-8C45-4D52788AA007}" name="roles" dataDxfId="47"/>
+    <tableColumn id="4" xr3:uid="{D684A6E0-2CB6-43AD-AA2A-978621E5D4DB}" name="activityTypeName" dataDxfId="46"/>
+    <tableColumn id="5" xr3:uid="{8BB7BDF5-9C51-428B-8F41-2D5551800DA8}" name="activityTypeId" dataDxfId="45">
       <calculatedColumnFormula>_xlfn.XLOOKUP(ParticipantTypeTable[[#This Row],[activityTypeName]],ActivityTypeTable[name], ActivityTypeTable[id],"",0,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{D21DFADD-72C9-48EF-9B97-94DCE941715E}" name=" min" dataDxfId="39"/>
-    <tableColumn id="9" xr3:uid="{2EB78418-4933-4BE7-848D-737A5AED6CD7}" name="max" dataDxfId="38"/>
+    <tableColumn id="8" xr3:uid="{D21DFADD-72C9-48EF-9B97-94DCE941715E}" name=" min" dataDxfId="44"/>
+    <tableColumn id="9" xr3:uid="{2EB78418-4933-4BE7-848D-737A5AED6CD7}" name="max" dataDxfId="43"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{15FD7229-441E-4FE3-AF45-908EA33D6E1A}" name="ParticipantTable" displayName="ParticipantTable" ref="A6:J7" totalsRowShown="0" headerRowDxfId="37" dataDxfId="35" headerRowBorderDxfId="36" tableBorderDxfId="34" totalsRowBorderDxfId="33">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{15FD7229-441E-4FE3-AF45-908EA33D6E1A}" name="ParticipantTable" displayName="ParticipantTable" ref="A6:J7" totalsRowShown="0" headerRowDxfId="42" dataDxfId="40" headerRowBorderDxfId="41" tableBorderDxfId="39" totalsRowBorderDxfId="38">
   <autoFilter ref="A6:J7" xr:uid="{15FD7229-441E-4FE3-AF45-908EA33D6E1A}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{652686EA-7035-4724-9CDA-D89B37DDB77D}" name="id" dataDxfId="32">
+    <tableColumn id="1" xr3:uid="{652686EA-7035-4724-9CDA-D89B37DDB77D}" name="id" dataDxfId="37">
       <calculatedColumnFormula>IF(ISBLANK(ParticipantTable[[#This Row],[activityName]]),"", ROW()-6)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{394ADFAF-FF0E-462F-BF79-96D9AFAC3CEA}" name="activityName" dataDxfId="31"/>
-    <tableColumn id="3" xr3:uid="{8FD18E64-E7FA-44AD-A7EC-413A12C07581}" name="userName" dataDxfId="30"/>
-    <tableColumn id="4" xr3:uid="{343F771A-82D0-4DC1-900F-370A7B1BECD0}" name="participantTypeName" dataDxfId="29"/>
-    <tableColumn id="5" xr3:uid="{BE01A539-C086-41E4-9971-BA82DB1D694F}" name="activityId" dataDxfId="28">
+    <tableColumn id="2" xr3:uid="{394ADFAF-FF0E-462F-BF79-96D9AFAC3CEA}" name="activityName" dataDxfId="36"/>
+    <tableColumn id="3" xr3:uid="{8FD18E64-E7FA-44AD-A7EC-413A12C07581}" name="userName" dataDxfId="35"/>
+    <tableColumn id="4" xr3:uid="{343F771A-82D0-4DC1-900F-370A7B1BECD0}" name="participantTypeName" dataDxfId="34"/>
+    <tableColumn id="5" xr3:uid="{BE01A539-C086-41E4-9971-BA82DB1D694F}" name="activityId" dataDxfId="33">
       <calculatedColumnFormula>_xlfn.XLOOKUP(ParticipantTable[[#This Row],[activityName]],ActivityTable[name], ActivityTable[id],"",0,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{0A7CDBA9-FD84-4CC8-8EDF-CD8D694398A9}" name="userId" dataDxfId="27">
+    <tableColumn id="6" xr3:uid="{0A7CDBA9-FD84-4CC8-8EDF-CD8D694398A9}" name="userId" dataDxfId="32">
       <calculatedColumnFormula>_xlfn.XLOOKUP(ParticipantTable[[#This Row],[userName]],UserTable[name],UserTable[id],"",0,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{F6E3050B-3F30-48C9-AAC7-FCAD98900424}" name="participantTypeId" dataDxfId="26">
+    <tableColumn id="7" xr3:uid="{F6E3050B-3F30-48C9-AAC7-FCAD98900424}" name="participantTypeId" dataDxfId="31">
       <calculatedColumnFormula>_xlfn.XLOOKUP(ParticipantTable[[#This Row],[participantTypeName]],ParticipantTypeTable[name],ParticipantTypeTable[id],"",0,1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{DACCFE94-858F-47FE-B4F6-B33E5374D14F}" name="hours" dataDxfId="25"/>
-    <tableColumn id="9" xr3:uid="{896BC859-D635-4695-B906-023A1E5FE6E6}" name="startAt" dataDxfId="24"/>
-    <tableColumn id="10" xr3:uid="{DFC6A317-6999-46F4-8CCD-ACD83FFB9F5E}" name="endAt" dataDxfId="23"/>
+    <tableColumn id="8" xr3:uid="{DACCFE94-858F-47FE-B4F6-B33E5374D14F}" name="hours" dataDxfId="30"/>
+    <tableColumn id="9" xr3:uid="{896BC859-D635-4695-B906-023A1E5FE6E6}" name="startAt" dataDxfId="29"/>
+    <tableColumn id="10" xr3:uid="{DFC6A317-6999-46F4-8CCD-ACD83FFB9F5E}" name="endAt" dataDxfId="28"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{E4DFEBB4-E470-43F4-9B57-CA71A40CB7EA}" name="CertificateTable" displayName="CertificateTable" ref="A6:B13" totalsRowShown="0" headerRowDxfId="22" headerRowBorderDxfId="21" tableBorderDxfId="20" totalsRowBorderDxfId="19">
-  <autoFilter ref="A6:B13" xr:uid="{E4DFEBB4-E470-43F4-9B57-CA71A40CB7EA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{E4DFEBB4-E470-43F4-9B57-CA71A40CB7EA}" name="CertificateTable" displayName="CertificateTable" ref="A6:B14" totalsRowShown="0" headerRowDxfId="119" headerRowBorderDxfId="118" tableBorderDxfId="117" totalsRowBorderDxfId="116">
+  <autoFilter ref="A6:B14" xr:uid="{E4DFEBB4-E470-43F4-9B57-CA71A40CB7EA}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{61038C46-43E9-4B35-96C1-CBBB1A87E834}" name="id" dataDxfId="18">
+    <tableColumn id="1" xr3:uid="{61038C46-43E9-4B35-96C1-CBBB1A87E834}" name="id" dataDxfId="115">
       <calculatedColumnFormula>IF(ISBLANK(CertificateTable[[#This Row],[name]]),"",ROW()-6)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{33957B68-51D0-43D0-8BD3-562B4F9472E0}" name="name" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{33957B68-51D0-43D0-8BD3-562B4F9472E0}" name="name" dataDxfId="114"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6500,21 +6607,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="48" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="107" t="s">
+    <row r="1" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="111" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -6525,7 +6632,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -6536,7 +6643,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
@@ -6547,7 +6654,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -6558,7 +6665,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>10</v>
       </c>
@@ -6569,7 +6676,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
@@ -6580,7 +6687,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>14</v>
       </c>
@@ -6591,7 +6698,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
@@ -6602,7 +6709,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>18</v>
       </c>
@@ -6613,7 +6720,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>20</v>
       </c>
@@ -6624,7 +6731,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>22</v>
       </c>
@@ -6635,7 +6742,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>24</v>
       </c>
@@ -6646,7 +6753,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>26</v>
       </c>
@@ -6657,7 +6764,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>28</v>
       </c>
@@ -6668,7 +6775,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>30</v>
       </c>
@@ -6679,22 +6786,22 @@
         <v>30</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
         <v>35</v>
       </c>
@@ -6710,7 +6817,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:J15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="16" customWidth="1"/>
     <col min="5" max="6" width="16" hidden="1" customWidth="1"/>
@@ -6718,35 +6825,35 @@
     <col min="8" max="10" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="104" t="s">
+    <row r="1" spans="1:10" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="108" t="s">
         <v>222</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="109"/>
-      <c r="D1" s="109"/>
-      <c r="E1" s="105"/>
-      <c r="F1" s="105"/>
-      <c r="G1" s="105"/>
-      <c r="H1" s="105"/>
-      <c r="I1" s="105"/>
-      <c r="J1" s="105"/>
-    </row>
-    <row r="2" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="106" t="s">
+      <c r="B1" s="113"/>
+      <c r="C1" s="113"/>
+      <c r="D1" s="113"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+      <c r="J1" s="109"/>
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="110" t="s">
         <v>223</v>
       </c>
-      <c r="B2" s="106"/>
-      <c r="C2" s="106"/>
-      <c r="D2" s="106"/>
-      <c r="E2" s="105"/>
-      <c r="F2" s="105"/>
-      <c r="G2" s="105"/>
-      <c r="H2" s="105"/>
-      <c r="I2" s="105"/>
-      <c r="J2" s="105"/>
-    </row>
-    <row r="3" spans="1:10" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="110"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="110"/>
+      <c r="E2" s="109"/>
+      <c r="F2" s="109"/>
+      <c r="G2" s="109"/>
+      <c r="H2" s="109"/>
+      <c r="I2" s="109"/>
+      <c r="J2" s="109"/>
+    </row>
+    <row r="3" spans="1:10" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>54</v>
       </c>
@@ -6778,7 +6885,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>56</v>
       </c>
@@ -6810,7 +6917,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>58</v>
       </c>
@@ -6842,7 +6949,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="23" t="s">
         <v>54</v>
       </c>
@@ -6874,7 +6981,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="str">
         <f>IF(ISBLANK(ParticipantTable[[#This Row],[activityName]]),"", ROW()-6)</f>
         <v/>
@@ -6898,14 +7005,14 @@
       <c r="I7" s="15"/>
       <c r="J7" s="38"/>
     </row>
-    <row r="8" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:J2"/>
@@ -6931,26 +7038,26 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="31.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="104" t="s">
+    <row r="1" spans="1:2" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="108" t="s">
         <v>238</v>
       </c>
-      <c r="B1" s="105"/>
-    </row>
-    <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="106" t="s">
+      <c r="B1" s="109"/>
+    </row>
+    <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="110" t="s">
         <v>239</v>
       </c>
-      <c r="B2" s="105"/>
-    </row>
-    <row r="3" spans="1:2" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="109"/>
+    </row>
+    <row r="3" spans="1:2" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>54</v>
       </c>
@@ -6958,7 +7065,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>56</v>
       </c>
@@ -6966,7 +7073,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>58</v>
       </c>
@@ -6974,7 +7081,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="23" t="s">
         <v>54</v>
       </c>
@@ -6982,7 +7089,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
         <v>368</v>
       </c>
@@ -6990,7 +7097,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
         <v>369</v>
       </c>
@@ -6998,7 +7105,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>370</v>
       </c>
@@ -7006,7 +7113,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>371</v>
       </c>
@@ -7014,7 +7121,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>372</v>
       </c>
@@ -7022,7 +7129,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>373</v>
       </c>
@@ -7030,7 +7137,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>374</v>
       </c>
@@ -7038,16 +7145,23 @@
         <v>244</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="80" t="s">
+        <v>472</v>
+      </c>
+      <c r="B14" s="81" t="s">
+        <v>473</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A2:B2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
@@ -7055,46 +7169,46 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="37.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="81.33203125" style="71" customWidth="1"/>
+    <col min="8" max="8" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="81.28515625" style="71" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="104" t="s">
+    <row r="1" spans="1:9" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="108" t="s">
         <v>245</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
-      <c r="F1" s="105"/>
-      <c r="G1" s="105"/>
-      <c r="H1" s="105"/>
-      <c r="I1" s="105"/>
-    </row>
-    <row r="2" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="106" t="s">
+      <c r="B1" s="113"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+      <c r="I1" s="109"/>
+    </row>
+    <row r="2" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="110" t="s">
         <v>246</v>
       </c>
-      <c r="B2" s="106"/>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
-      <c r="F2" s="105"/>
-      <c r="G2" s="105"/>
-      <c r="H2" s="105"/>
-      <c r="I2" s="105"/>
-    </row>
-    <row r="3" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="B2" s="110"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="109"/>
+      <c r="E2" s="109"/>
+      <c r="F2" s="109"/>
+      <c r="G2" s="109"/>
+      <c r="H2" s="109"/>
+      <c r="I2" s="109"/>
+    </row>
+    <row r="3" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>54</v>
       </c>
@@ -7123,7 +7237,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>56</v>
       </c>
@@ -7152,7 +7266,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>58</v>
       </c>
@@ -7181,7 +7295,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="23" t="s">
         <v>54</v>
       </c>
@@ -7210,7 +7324,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="66" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
         <v>375</v>
       </c>
@@ -7235,10 +7349,10 @@
         <v/>
       </c>
       <c r="I7" s="70" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="108" x14ac:dyDescent="0.35">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="131.25" x14ac:dyDescent="0.3">
       <c r="A8" s="19" t="s">
         <v>376</v>
       </c>
@@ -7262,10 +7376,10 @@
         <v>422</v>
       </c>
       <c r="I8" s="67" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="132" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
         <v>377</v>
       </c>
@@ -7290,10 +7404,10 @@
         <v>49a226e4-b8bc-4885-a1ba-f273c63ab27f</v>
       </c>
       <c r="I9" s="101" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="97.2" x14ac:dyDescent="0.35">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="108" x14ac:dyDescent="0.35">
       <c r="A10" s="19" t="s">
         <v>378</v>
       </c>
@@ -7318,10 +7432,10 @@
         <v>09642418-bf20-4666-82d0-b788c9b0ed3c</v>
       </c>
       <c r="I10" s="102" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="115.5" x14ac:dyDescent="0.3">
       <c r="A11" s="19" t="s">
         <v>379</v>
       </c>
@@ -7346,25 +7460,25 @@
         <v>5b8a57a3-4284-4a02-a7e4-cc2181a9aad4</v>
       </c>
       <c r="I11" s="103" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I12"/>
     </row>
-    <row r="13" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I13"/>
     </row>
-    <row r="14" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I14"/>
     </row>
-    <row r="15" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="I15"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="I16"/>
     </row>
-    <row r="17" spans="9:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="9:9" x14ac:dyDescent="0.25">
       <c r="I17"/>
     </row>
   </sheetData>
@@ -7393,37 +7507,37 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="29.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="101.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="101.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="104" t="s">
+    <row r="1" spans="1:6" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="108" t="s">
         <v>257</v>
       </c>
-      <c r="B1" s="104"/>
-      <c r="C1" s="104"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
-      <c r="F1" s="105"/>
-    </row>
-    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="106" t="s">
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+    </row>
+    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="110" t="s">
         <v>258</v>
       </c>
-      <c r="B2" s="106"/>
-      <c r="C2" s="106"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
-      <c r="F2" s="105"/>
-    </row>
-    <row r="3" spans="1:6" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="110"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="109"/>
+      <c r="E2" s="109"/>
+      <c r="F2" s="109"/>
+    </row>
+    <row r="3" spans="1:6" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>54</v>
       </c>
@@ -7443,7 +7557,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>56</v>
       </c>
@@ -7463,7 +7577,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>58</v>
       </c>
@@ -7483,7 +7597,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="46" t="s">
         <v>54</v>
       </c>
@@ -7503,7 +7617,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
         <v>380</v>
       </c>
@@ -7525,14 +7639,14 @@
         <v>281</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
@@ -7556,37 +7670,37 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:G15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="9.88671875" customWidth="1"/>
+    <col min="5" max="5" width="9.85546875" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="16" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="104" t="s">
+    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="108" t="s">
         <v>265</v>
       </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
-      <c r="F1" s="105"/>
-      <c r="G1" s="105"/>
-    </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="106" t="s">
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="110" t="s">
         <v>266</v>
       </c>
-      <c r="B2" s="105"/>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
-      <c r="F2" s="105"/>
-      <c r="G2" s="105"/>
-    </row>
-    <row r="3" spans="1:7" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="109"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="109"/>
+      <c r="E2" s="109"/>
+      <c r="F2" s="109"/>
+      <c r="G2" s="109"/>
+    </row>
+    <row r="3" spans="1:7" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>54</v>
       </c>
@@ -7609,7 +7723,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>56</v>
       </c>
@@ -7632,7 +7746,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="49" t="s">
         <v>58</v>
       </c>
@@ -7655,7 +7769,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>54</v>
       </c>
@@ -7676,7 +7790,7 @@
       </c>
       <c r="G6" s="19"/>
     </row>
-    <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="83" t="s">
         <v>381</v>
       </c>
@@ -7698,7 +7812,7 @@
       </c>
       <c r="G7" s="86"/>
     </row>
-    <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="87" t="s">
         <v>384</v>
       </c>
@@ -7721,25 +7835,25 @@
       </c>
       <c r="G8" s="19"/>
     </row>
-    <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G9" s="2"/>
     </row>
-    <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G10" s="3"/>
     </row>
-    <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G11" s="2"/>
     </row>
-    <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G12" s="3"/>
     </row>
-    <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G13" s="2"/>
     </row>
-    <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G14" s="3"/>
     </row>
-    <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G15" s="2"/>
     </row>
   </sheetData>
@@ -7757,24 +7871,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="108" t="s">
+    <row r="1" spans="1:6" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="112" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
-      <c r="F1" s="105"/>
-    </row>
-    <row r="2" spans="1:6" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+    </row>
+    <row r="2" spans="1:6" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>37</v>
       </c>
@@ -7785,7 +7899,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>40</v>
       </c>
@@ -7796,7 +7910,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>43</v>
       </c>
@@ -7807,7 +7921,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>46</v>
       </c>
@@ -7818,7 +7932,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C6" s="9" t="s">
         <v>49</v>
       </c>
@@ -7826,7 +7940,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="E7" s="9" t="s">
         <v>51</v>
       </c>
@@ -7842,25 +7956,25 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="109" t="s">
+    <row r="1" spans="1:2" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="113" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="105"/>
-    </row>
-    <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="106" t="s">
+      <c r="B1" s="109"/>
+    </row>
+    <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="110" t="s">
         <v>53</v>
       </c>
-      <c r="B2" s="105"/>
-    </row>
-    <row r="3" spans="1:2" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="109"/>
+    </row>
+    <row r="3" spans="1:2" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>54</v>
       </c>
@@ -7868,7 +7982,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>56</v>
       </c>
@@ -7876,7 +7990,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>58</v>
       </c>
@@ -7884,7 +7998,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="6" spans="1:2" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="23" t="s">
         <v>54</v>
       </c>
@@ -7892,7 +8006,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>320</v>
       </c>
@@ -7900,7 +8014,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>321</v>
       </c>
@@ -7908,13 +8022,13 @@
         <v>62</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="10" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="12" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:B2"/>
@@ -7930,33 +8044,33 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="20.6640625" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="20.7109375" customWidth="1"/>
     <col min="4" max="5" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="109" t="s">
+    <row r="1" spans="1:5" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="113" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
-    </row>
-    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="106" t="s">
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+    </row>
+    <row r="2" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="110" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="105"/>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
-    </row>
-    <row r="3" spans="1:5" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="109"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="109"/>
+      <c r="E2" s="109"/>
+    </row>
+    <row r="3" spans="1:5" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>54</v>
       </c>
@@ -7973,7 +8087,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>56</v>
       </c>
@@ -7990,7 +8104,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>58</v>
       </c>
@@ -8007,7 +8121,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="23" t="s">
         <v>54</v>
       </c>
@@ -8024,7 +8138,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="34" t="s">
         <v>314</v>
       </c>
@@ -8042,7 +8156,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="34" t="s">
         <v>315</v>
       </c>
@@ -8060,7 +8174,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="34" t="s">
         <v>316</v>
       </c>
@@ -8078,7 +8192,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="34" t="s">
         <v>317</v>
       </c>
@@ -8096,7 +8210,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="34" t="s">
         <v>318</v>
       </c>
@@ -8114,7 +8228,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="34" t="s">
         <v>319</v>
       </c>
@@ -8132,9 +8246,9 @@
         <v>81</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
@@ -8158,60 +8272,60 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:O36"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AJ36"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="36.33203125" customWidth="1"/>
-    <col min="4" max="4" width="36.6640625" customWidth="1"/>
+    <col min="3" max="3" width="36.28515625" customWidth="1"/>
+    <col min="4" max="4" width="36.7109375" customWidth="1"/>
     <col min="5" max="5" width="17" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="25.109375" customWidth="1"/>
-    <col min="8" max="8" width="9.6640625" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="13.44140625" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="15.5546875" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="25.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.7109375" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" hidden="1" customWidth="1"/>
     <col min="11" max="12" width="16" customWidth="1"/>
     <col min="13" max="13" width="37" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="19.88671875" customWidth="1"/>
+    <col min="14" max="14" width="19.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="104" t="s">
+    <row r="1" spans="1:36" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="108" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="104"/>
-      <c r="C1" s="104"/>
-      <c r="D1" s="104"/>
-      <c r="E1" s="104"/>
-      <c r="F1" s="104"/>
-      <c r="G1" s="104"/>
-      <c r="H1" s="104"/>
-      <c r="I1" s="104"/>
-      <c r="J1" s="104"/>
-      <c r="K1" s="104"/>
-      <c r="L1" s="104"/>
-      <c r="M1" s="104"/>
-      <c r="N1" s="104"/>
-    </row>
-    <row r="2" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="110" t="s">
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
+      <c r="F1" s="108"/>
+      <c r="G1" s="108"/>
+      <c r="H1" s="108"/>
+      <c r="I1" s="108"/>
+      <c r="J1" s="108"/>
+      <c r="K1" s="108"/>
+      <c r="L1" s="108"/>
+      <c r="M1" s="108"/>
+      <c r="N1" s="108"/>
+    </row>
+    <row r="2" spans="1:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="114" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="110"/>
-      <c r="C2" s="110"/>
-      <c r="D2" s="110"/>
-      <c r="E2" s="110"/>
-      <c r="F2" s="110"/>
-      <c r="G2" s="110"/>
-      <c r="H2" s="110"/>
-      <c r="I2" s="110"/>
-      <c r="J2" s="110"/>
-      <c r="K2" s="110"/>
-      <c r="L2" s="110"/>
-      <c r="M2" s="110"/>
-      <c r="N2" s="110"/>
-    </row>
-    <row r="3" spans="1:15" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="114"/>
+      <c r="C2" s="114"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="114"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="114"/>
+      <c r="I2" s="114"/>
+      <c r="J2" s="114"/>
+      <c r="K2" s="114"/>
+      <c r="L2" s="114"/>
+      <c r="M2" s="114"/>
+      <c r="N2" s="114"/>
+    </row>
+    <row r="3" spans="1:36" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>54</v>
       </c>
@@ -8255,7 +8369,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>70</v>
       </c>
@@ -8299,7 +8413,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>98</v>
       </c>
@@ -8343,7 +8457,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A6" s="34" t="s">
         <v>54</v>
       </c>
@@ -8387,14 +8501,14 @@
         <v>110</v>
       </c>
     </row>
-    <row r="7" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
         <v>287</v>
       </c>
       <c r="B7" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="104" t="s">
         <v>111</v>
       </c>
       <c r="D7" s="42" t="s">
@@ -8418,15 +8532,22 @@
         <f>_xlfn.XLOOKUP(UserTable[[#This Row],[academicDegreeName]], ADegreeTable[name], ADegreeTable[id],"",0,1)</f>
         <v/>
       </c>
-    </row>
-    <row r="8" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AI7" s="104" t="s">
+        <v>111</v>
+      </c>
+      <c r="AJ7" t="str">
+        <f>PROPER($AI7)</f>
+        <v xml:space="preserve">Daniela Alejandra Ramírez Ñonque </v>
+      </c>
+    </row>
+    <row r="8" spans="1:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
         <v>288</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="105" t="s">
         <v>113</v>
       </c>
       <c r="D8" s="57" t="s">
@@ -8453,16 +8574,23 @@
       <c r="N8" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AI8" s="106" t="s">
+        <v>113</v>
+      </c>
+      <c r="AJ8" t="str">
+        <f t="shared" ref="AJ8:AJ36" si="0">PROPER($AI8)</f>
+        <v>Tamara Francisca Otzen Hernandez</v>
+      </c>
+    </row>
+    <row r="9" spans="1:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>289</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C9" s="18" t="s">
-        <v>118</v>
+      <c r="C9" s="104" t="s">
+        <v>446</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>119</v>
@@ -8485,16 +8613,23 @@
         <f>_xlfn.XLOOKUP(UserTable[[#This Row],[academicDegreeName]], ADegreeTable[name], ADegreeTable[id],"",0,1)</f>
         <v/>
       </c>
-    </row>
-    <row r="10" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AI9" s="104" t="s">
+        <v>118</v>
+      </c>
+      <c r="AJ9" t="str">
+        <f t="shared" si="0"/>
+        <v>Louise Zanella Martins</v>
+      </c>
+    </row>
+    <row r="10" spans="1:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>290</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>121</v>
+      <c r="C10" s="105" t="s">
+        <v>447</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>122</v>
@@ -8517,16 +8652,23 @@
         <f>_xlfn.XLOOKUP(UserTable[[#This Row],[academicDegreeName]], ADegreeTable[name], ADegreeTable[id],"",0,1)</f>
         <v/>
       </c>
-    </row>
-    <row r="11" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AI10" s="106" t="s">
+        <v>121</v>
+      </c>
+      <c r="AJ10" t="str">
+        <f t="shared" si="0"/>
+        <v>Rodrigo Rivera Concha</v>
+      </c>
+    </row>
+    <row r="11" spans="1:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>291</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="C11" s="18" t="s">
-        <v>397</v>
+      <c r="C11" s="104" t="s">
+        <v>448</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>123</v>
@@ -8549,14 +8691,21 @@
         <f>_xlfn.XLOOKUP(UserTable[[#This Row],[academicDegreeName]], ADegreeTable[name], ADegreeTable[id],"",0,1)</f>
         <v/>
       </c>
-    </row>
-    <row r="12" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AI11" s="104" t="s">
+        <v>397</v>
+      </c>
+      <c r="AJ11" t="str">
+        <f t="shared" si="0"/>
+        <v>Javier Hernan Alarcon Roa</v>
+      </c>
+    </row>
+    <row r="12" spans="1:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>292</v>
       </c>
       <c r="B12" s="2"/>
-      <c r="C12" s="78" t="s">
-        <v>395</v>
+      <c r="C12" s="106" t="s">
+        <v>449</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>125</v>
@@ -8579,16 +8728,23 @@
         <f>_xlfn.XLOOKUP(UserTable[[#This Row],[academicDegreeName]], ADegreeTable[name], ADegreeTable[id],"",0,1)</f>
         <v/>
       </c>
-    </row>
-    <row r="13" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AI12" s="106" t="s">
+        <v>395</v>
+      </c>
+      <c r="AJ12" t="str">
+        <f t="shared" si="0"/>
+        <v>Lorena Carlota Albarracin Navas</v>
+      </c>
+    </row>
+    <row r="13" spans="1:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>293</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C13" s="18" t="s">
-        <v>396</v>
+      <c r="C13" s="104" t="s">
+        <v>450</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>127</v>
@@ -8611,16 +8767,23 @@
         <f>_xlfn.XLOOKUP(UserTable[[#This Row],[academicDegreeName]], ADegreeTable[name], ADegreeTable[id],"",0,1)</f>
         <v/>
       </c>
-    </row>
-    <row r="14" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AI13" s="104" t="s">
+        <v>396</v>
+      </c>
+      <c r="AJ13" t="str">
+        <f t="shared" si="0"/>
+        <v>Javier Ignacio Arriagada Gacitúa</v>
+      </c>
+    </row>
+    <row r="14" spans="1:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
         <v>294</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C14" s="78" t="s">
-        <v>398</v>
+      <c r="C14" s="106" t="s">
+        <v>451</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>129</v>
@@ -8644,16 +8807,23 @@
         <v/>
       </c>
       <c r="O14" s="51"/>
-    </row>
-    <row r="15" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AI14" s="106" t="s">
+        <v>398</v>
+      </c>
+      <c r="AJ14" t="str">
+        <f t="shared" si="0"/>
+        <v>Sandra Paulina Catalan Monsalve</v>
+      </c>
+    </row>
+    <row r="15" spans="1:36" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="34" t="s">
         <v>295</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C15" s="18" t="s">
-        <v>399</v>
+      <c r="C15" s="104" t="s">
+        <v>452</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>131</v>
@@ -8676,14 +8846,21 @@
         <f>_xlfn.XLOOKUP(UserTable[[#This Row],[academicDegreeName]], ADegreeTable[name], ADegreeTable[id],"",0,1)</f>
         <v/>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="AI15" s="104" t="s">
+        <v>399</v>
+      </c>
+      <c r="AJ15" t="str">
+        <f t="shared" si="0"/>
+        <v>Hugo Alfredo Delgado Muñoz</v>
+      </c>
+    </row>
+    <row r="16" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>296</v>
       </c>
       <c r="B16" s="2"/>
-      <c r="C16" s="78" t="s">
-        <v>400</v>
+      <c r="C16" s="106" t="s">
+        <v>453</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>132</v>
@@ -8706,14 +8883,21 @@
         <f>_xlfn.XLOOKUP(UserTable[[#This Row],[academicDegreeName]], ADegreeTable[name], ADegreeTable[id],"",0,1)</f>
         <v/>
       </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="AI16" s="106" t="s">
+        <v>400</v>
+      </c>
+      <c r="AJ16" t="str">
+        <f t="shared" si="0"/>
+        <v>Galo Ruben Duque Proaño</v>
+      </c>
+    </row>
+    <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" s="72" t="s">
         <v>297</v>
       </c>
       <c r="B17" s="54"/>
-      <c r="C17" s="79" t="s">
-        <v>401</v>
+      <c r="C17" s="77" t="s">
+        <v>454</v>
       </c>
       <c r="D17" s="54" t="s">
         <v>133</v>
@@ -8738,16 +8922,23 @@
         <f>_xlfn.XLOOKUP(UserTable[[#This Row],[academicDegreeName]], ADegreeTable[name], ADegreeTable[id],"",0,1)</f>
         <v/>
       </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="AI17" s="77" t="s">
+        <v>401</v>
+      </c>
+      <c r="AJ17" t="str">
+        <f t="shared" si="0"/>
+        <v>Maria Elena Espinosa Gonzalez</v>
+      </c>
+    </row>
+    <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" s="53" t="s">
         <v>298</v>
       </c>
       <c r="B18" s="54" t="s">
         <v>134</v>
       </c>
-      <c r="C18" s="79" t="s">
-        <v>402</v>
+      <c r="C18" s="77" t="s">
+        <v>455</v>
       </c>
       <c r="D18" s="54" t="s">
         <v>135</v>
@@ -8772,14 +8963,21 @@
         <f>_xlfn.XLOOKUP(UserTable[[#This Row],[academicDegreeName]], ADegreeTable[name], ADegreeTable[id],"",0,1)</f>
         <v/>
       </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="AI18" s="77" t="s">
+        <v>402</v>
+      </c>
+      <c r="AJ18" t="str">
+        <f t="shared" si="0"/>
+        <v>Mirta Andrea Espinoza Cid</v>
+      </c>
+    </row>
+    <row r="19" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" s="72" t="s">
         <v>299</v>
       </c>
       <c r="B19" s="54"/>
-      <c r="C19" s="79" t="s">
-        <v>403</v>
+      <c r="C19" s="77" t="s">
+        <v>456</v>
       </c>
       <c r="D19" s="54" t="s">
         <v>136</v>
@@ -8804,16 +9002,23 @@
         <f>_xlfn.XLOOKUP(UserTable[[#This Row],[academicDegreeName]], ADegreeTable[name], ADegreeTable[id],"",0,1)</f>
         <v/>
       </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="AI19" s="77" t="s">
+        <v>403</v>
+      </c>
+      <c r="AJ19" t="str">
+        <f t="shared" si="0"/>
+        <v>Maria Fernanda Garcia Aguilera</v>
+      </c>
+    </row>
+    <row r="20" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" s="72" t="s">
         <v>300</v>
       </c>
       <c r="B20" s="54" t="s">
         <v>137</v>
       </c>
-      <c r="C20" s="79" t="s">
-        <v>404</v>
+      <c r="C20" s="77" t="s">
+        <v>457</v>
       </c>
       <c r="D20" s="54" t="s">
         <v>138</v>
@@ -8838,14 +9043,21 @@
         <f>_xlfn.XLOOKUP(UserTable[[#This Row],[academicDegreeName]], ADegreeTable[name], ADegreeTable[id],"",0,1)</f>
         <v/>
       </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="AI20" s="77" t="s">
+        <v>404</v>
+      </c>
+      <c r="AJ20" t="str">
+        <f t="shared" si="0"/>
+        <v>Álvaro Ignacio Godoy Díaz</v>
+      </c>
+    </row>
+    <row r="21" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A21" s="53" t="s">
         <v>301</v>
       </c>
       <c r="B21" s="54"/>
-      <c r="C21" s="79" t="s">
-        <v>405</v>
+      <c r="C21" s="77" t="s">
+        <v>458</v>
       </c>
       <c r="D21" s="54" t="s">
         <v>139</v>
@@ -8870,14 +9082,21 @@
         <f>_xlfn.XLOOKUP(UserTable[[#This Row],[academicDegreeName]], ADegreeTable[name], ADegreeTable[id],"",0,1)</f>
         <v/>
       </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="AI21" s="77" t="s">
+        <v>405</v>
+      </c>
+      <c r="AJ21" t="str">
+        <f t="shared" si="0"/>
+        <v>Enmanuel Isidoro Guerrero Quiroz</v>
+      </c>
+    </row>
+    <row r="22" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" s="72" t="s">
         <v>302</v>
       </c>
       <c r="B22" s="54"/>
-      <c r="C22" s="79" t="s">
-        <v>406</v>
+      <c r="C22" s="77" t="s">
+        <v>459</v>
       </c>
       <c r="D22" s="54" t="s">
         <v>140</v>
@@ -8902,16 +9121,23 @@
         <f>_xlfn.XLOOKUP(UserTable[[#This Row],[academicDegreeName]], ADegreeTable[name], ADegreeTable[id],"",0,1)</f>
         <v/>
       </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="AI22" s="77" t="s">
+        <v>406</v>
+      </c>
+      <c r="AJ22" t="str">
+        <f t="shared" si="0"/>
+        <v>Juan Pablo Holguin Carvajal</v>
+      </c>
+    </row>
+    <row r="23" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" s="53" t="s">
         <v>303</v>
       </c>
       <c r="B23" s="79" t="s">
-        <v>442</v>
-      </c>
-      <c r="C23" s="79" t="s">
-        <v>407</v>
+        <v>441</v>
+      </c>
+      <c r="C23" s="77" t="s">
+        <v>460</v>
       </c>
       <c r="D23" s="54" t="s">
         <v>141</v>
@@ -8936,16 +9162,23 @@
         <f>_xlfn.XLOOKUP(UserTable[[#This Row],[academicDegreeName]], ADegreeTable[name], ADegreeTable[id],"",0,1)</f>
         <v/>
       </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="AI23" s="77" t="s">
+        <v>407</v>
+      </c>
+      <c r="AJ23" t="str">
+        <f t="shared" si="0"/>
+        <v>Mariela Alejandra Landero Fuentes</v>
+      </c>
+    </row>
+    <row r="24" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24" s="53" t="s">
         <v>304</v>
       </c>
       <c r="B24" s="54" t="s">
         <v>142</v>
       </c>
-      <c r="C24" s="79" t="s">
-        <v>408</v>
+      <c r="C24" s="77" t="s">
+        <v>461</v>
       </c>
       <c r="D24" s="54" t="s">
         <v>143</v>
@@ -8970,16 +9203,23 @@
         <f>_xlfn.XLOOKUP(UserTable[[#This Row],[academicDegreeName]], ADegreeTable[name], ADegreeTable[id],"",0,1)</f>
         <v/>
       </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="AI24" s="77" t="s">
+        <v>408</v>
+      </c>
+      <c r="AJ24" t="str">
+        <f t="shared" si="0"/>
+        <v>Nicolás Ignacio Lara Salas</v>
+      </c>
+    </row>
+    <row r="25" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A25" s="53" t="s">
         <v>305</v>
       </c>
       <c r="B25" s="79" t="s">
-        <v>441</v>
-      </c>
-      <c r="C25" s="79" t="s">
-        <v>409</v>
+        <v>440</v>
+      </c>
+      <c r="C25" s="77" t="s">
+        <v>462</v>
       </c>
       <c r="D25" s="54" t="s">
         <v>145</v>
@@ -9004,14 +9244,21 @@
         <f>_xlfn.XLOOKUP(UserTable[[#This Row],[academicDegreeName]], ADegreeTable[name], ADegreeTable[id],"",0,1)</f>
         <v/>
       </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="AI25" s="77" t="s">
+        <v>409</v>
+      </c>
+      <c r="AJ25" t="str">
+        <f t="shared" si="0"/>
+        <v>Pamela Constanza Lavados Romo</v>
+      </c>
+    </row>
+    <row r="26" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A26" s="72" t="s">
         <v>306</v>
       </c>
       <c r="B26" s="54"/>
-      <c r="C26" s="79" t="s">
-        <v>410</v>
+      <c r="C26" s="77" t="s">
+        <v>463</v>
       </c>
       <c r="D26" s="54" t="s">
         <v>146</v>
@@ -9036,14 +9283,21 @@
         <f>_xlfn.XLOOKUP(UserTable[[#This Row],[academicDegreeName]], ADegreeTable[name], ADegreeTable[id],"",0,1)</f>
         <v/>
       </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="AI26" s="77" t="s">
+        <v>410</v>
+      </c>
+      <c r="AJ26" t="str">
+        <f t="shared" si="0"/>
+        <v>Miriann Alexandra Mora Verdugo</v>
+      </c>
+    </row>
+    <row r="27" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A27" s="72" t="s">
         <v>307</v>
       </c>
       <c r="B27" s="54"/>
-      <c r="C27" s="79" t="s">
-        <v>411</v>
+      <c r="C27" s="77" t="s">
+        <v>464</v>
       </c>
       <c r="D27" s="54" t="s">
         <v>147</v>
@@ -9068,16 +9322,23 @@
         <f>_xlfn.XLOOKUP(UserTable[[#This Row],[academicDegreeName]], ADegreeTable[name], ADegreeTable[id],"",0,1)</f>
         <v/>
       </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="AI27" s="77" t="s">
+        <v>411</v>
+      </c>
+      <c r="AJ27" t="str">
+        <f t="shared" si="0"/>
+        <v>Eudoxia Georgina Muñoz Ortiz</v>
+      </c>
+    </row>
+    <row r="28" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A28" s="53" t="s">
         <v>308</v>
       </c>
       <c r="B28" s="54" t="s">
         <v>148</v>
       </c>
-      <c r="C28" s="79" t="s">
-        <v>412</v>
+      <c r="C28" s="77" t="s">
+        <v>465</v>
       </c>
       <c r="D28" s="54" t="s">
         <v>149</v>
@@ -9102,16 +9363,23 @@
         <f>_xlfn.XLOOKUP(UserTable[[#This Row],[academicDegreeName]], ADegreeTable[name], ADegreeTable[id],"",0,1)</f>
         <v/>
       </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="AI28" s="77" t="s">
+        <v>412</v>
+      </c>
+      <c r="AJ28" t="str">
+        <f t="shared" si="0"/>
+        <v>Orieta Del Pilar Navarrete Fernandez</v>
+      </c>
+    </row>
+    <row r="29" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A29" s="53" t="s">
         <v>309</v>
       </c>
       <c r="B29" s="54" t="s">
         <v>150</v>
       </c>
-      <c r="C29" s="79" t="s">
-        <v>413</v>
+      <c r="C29" s="77" t="s">
+        <v>466</v>
       </c>
       <c r="D29" s="54" t="s">
         <v>151</v>
@@ -9136,14 +9404,21 @@
         <f>_xlfn.XLOOKUP(UserTable[[#This Row],[academicDegreeName]], ADegreeTable[name], ADegreeTable[id],"",0,1)</f>
         <v/>
       </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="AI29" s="77" t="s">
+        <v>413</v>
+      </c>
+      <c r="AJ29" t="str">
+        <f t="shared" si="0"/>
+        <v>Guissela Romane Quiroz Sievers</v>
+      </c>
+    </row>
+    <row r="30" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A30" s="72" t="s">
         <v>310</v>
       </c>
       <c r="B30" s="54"/>
-      <c r="C30" s="79" t="s">
-        <v>414</v>
+      <c r="C30" s="77" t="s">
+        <v>467</v>
       </c>
       <c r="D30" s="54" t="s">
         <v>152</v>
@@ -9168,14 +9443,21 @@
         <f>_xlfn.XLOOKUP(UserTable[[#This Row],[academicDegreeName]], ADegreeTable[name], ADegreeTable[id],"",0,1)</f>
         <v/>
       </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="AI30" s="77" t="s">
+        <v>414</v>
+      </c>
+      <c r="AJ30" t="str">
+        <f t="shared" si="0"/>
+        <v>Josue David Rivadeneira Dueñas</v>
+      </c>
+    </row>
+    <row r="31" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" s="53" t="s">
         <v>311</v>
       </c>
       <c r="B31" s="54"/>
-      <c r="C31" s="79" t="s">
-        <v>416</v>
+      <c r="C31" s="77" t="s">
+        <v>468</v>
       </c>
       <c r="D31" s="54" t="s">
         <v>153</v>
@@ -9200,16 +9482,23 @@
         <f>_xlfn.XLOOKUP(UserTable[[#This Row],[academicDegreeName]], ADegreeTable[name], ADegreeTable[id],"",0,1)</f>
         <v/>
       </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="AI31" s="77" t="s">
+        <v>416</v>
+      </c>
+      <c r="AJ31" t="str">
+        <f t="shared" si="0"/>
+        <v>Carla Marina Salgado Castillo</v>
+      </c>
+    </row>
+    <row r="32" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A32" s="53" t="s">
         <v>312</v>
       </c>
       <c r="B32" s="54" t="s">
         <v>154</v>
       </c>
-      <c r="C32" s="79" t="s">
-        <v>417</v>
+      <c r="C32" s="77" t="s">
+        <v>469</v>
       </c>
       <c r="D32" s="54" t="s">
         <v>155</v>
@@ -9234,16 +9523,23 @@
         <f>_xlfn.XLOOKUP(UserTable[[#This Row],[academicDegreeName]], ADegreeTable[name], ADegreeTable[id],"",0,1)</f>
         <v/>
       </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="AI32" s="77" t="s">
+        <v>417</v>
+      </c>
+      <c r="AJ32" t="str">
+        <f t="shared" si="0"/>
+        <v>Sergio Antonio Sotelo Hernandez</v>
+      </c>
+    </row>
+    <row r="33" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A33" s="53" t="s">
         <v>313</v>
       </c>
       <c r="B33" s="54" t="s">
         <v>156</v>
       </c>
-      <c r="C33" s="79" t="s">
-        <v>418</v>
+      <c r="C33" s="77" t="s">
+        <v>470</v>
       </c>
       <c r="D33" s="54" t="s">
         <v>157</v>
@@ -9268,15 +9564,22 @@
         <f>_xlfn.XLOOKUP(UserTable[[#This Row],[academicDegreeName]], ADegreeTable[name], ADegreeTable[id],"",0,1)</f>
         <v/>
       </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="AI33" s="77" t="s">
+        <v>418</v>
+      </c>
+      <c r="AJ33" t="str">
+        <f t="shared" si="0"/>
+        <v>Paulina Antonia Vasquez Aguilar</v>
+      </c>
+    </row>
+    <row r="34" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A34" s="59" t="s">
         <v>428</v>
       </c>
       <c r="B34" s="81" t="s">
         <v>429</v>
       </c>
-      <c r="C34" s="81" t="s">
+      <c r="C34" s="98" t="s">
         <v>430</v>
       </c>
       <c r="D34" s="95" t="s">
@@ -9305,15 +9608,22 @@
       <c r="N34" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="AI34" s="107" t="s">
+        <v>430</v>
+      </c>
+      <c r="AJ34" t="str">
+        <f t="shared" si="0"/>
+        <v>Tomás Alonso Bravo Cañete</v>
+      </c>
+    </row>
+    <row r="35" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A35" s="80" t="s">
         <v>432</v>
       </c>
       <c r="B35" s="81" t="s">
         <v>435</v>
       </c>
-      <c r="C35" s="81" t="s">
+      <c r="C35" s="98" t="s">
         <v>433</v>
       </c>
       <c r="D35" s="95" t="s">
@@ -9339,19 +9649,24 @@
         <f>_xlfn.XLOOKUP(UserTable[[#This Row],[academicDegreeName]], ADegreeTable[name], ADegreeTable[id],"",0,1)</f>
         <v/>
       </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="AI35" s="107" t="s">
+        <v>433</v>
+      </c>
+      <c r="AJ35" t="str">
+        <f t="shared" si="0"/>
+        <v>Isidora Acevedo</v>
+      </c>
+    </row>
+    <row r="36" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A36" s="80" t="s">
         <v>436</v>
       </c>
-      <c r="B36" s="81" t="s">
+      <c r="B36" s="81"/>
+      <c r="C36" s="98" t="s">
         <v>437</v>
       </c>
-      <c r="C36" s="81" t="s">
+      <c r="D36" s="95" t="s">
         <v>438</v>
-      </c>
-      <c r="D36" s="95" t="s">
-        <v>439</v>
       </c>
       <c r="E36" s="92" t="b">
         <v>0</v>
@@ -9372,6 +9687,13 @@
       <c r="M36" t="str">
         <f>_xlfn.XLOOKUP(UserTable[[#This Row],[academicDegreeName]], ADegreeTable[name], ADegreeTable[id],"",0,1)</f>
         <v/>
+      </c>
+      <c r="AI36" s="107" t="s">
+        <v>437</v>
+      </c>
+      <c r="AJ36" t="str">
+        <f t="shared" si="0"/>
+        <v>Super Administrador</v>
       </c>
     </row>
   </sheetData>
@@ -9407,36 +9729,36 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
-    <col min="4" max="4" width="15.88671875" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="104" t="s">
+    <row r="1" spans="1:6" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="108" t="s">
         <v>158</v>
       </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
-      <c r="F1" s="105"/>
-    </row>
-    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="106" t="s">
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+    </row>
+    <row r="2" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="110" t="s">
         <v>159</v>
       </c>
-      <c r="B2" s="105"/>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
-      <c r="F2" s="105"/>
-    </row>
-    <row r="3" spans="1:6" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="109"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="109"/>
+      <c r="E2" s="109"/>
+      <c r="F2" s="109"/>
+    </row>
+    <row r="3" spans="1:6" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>54</v>
       </c>
@@ -9456,7 +9778,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>56</v>
       </c>
@@ -9476,7 +9798,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="33.75" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>58</v>
       </c>
@@ -9496,7 +9818,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="23" t="s">
         <v>54</v>
       </c>
@@ -9516,7 +9838,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="34" t="s">
         <v>322</v>
       </c>
@@ -9537,7 +9859,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="34" t="s">
         <v>323</v>
       </c>
@@ -9558,7 +9880,7 @@
         <v>43891</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="34" t="s">
         <v>324</v>
       </c>
@@ -9579,7 +9901,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="34" t="s">
         <v>325</v>
       </c>
@@ -9600,7 +9922,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="34" t="s">
         <v>326</v>
       </c>
@@ -9621,7 +9943,7 @@
         <v>44986</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="34" t="s">
         <v>327</v>
       </c>
@@ -9642,7 +9964,7 @@
         <v>43160</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="34" t="s">
         <v>328</v>
       </c>
@@ -9663,7 +9985,7 @@
         <v>43891</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="34" t="s">
         <v>329</v>
       </c>
@@ -9684,7 +10006,7 @@
         <v>45352</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="34" t="s">
         <v>330</v>
       </c>
@@ -9705,7 +10027,7 @@
         <v>44256</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="34" t="s">
         <v>331</v>
       </c>
@@ -9726,7 +10048,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="53" t="s">
         <v>332</v>
       </c>
@@ -9747,7 +10069,7 @@
         <v>43525</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="53" t="s">
         <v>333</v>
       </c>
@@ -9768,7 +10090,7 @@
         <v>44256</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="53" t="s">
         <v>334</v>
       </c>
@@ -9789,7 +10111,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="53" t="s">
         <v>335</v>
       </c>
@@ -9810,7 +10132,7 @@
         <v>45717</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="72" t="s">
         <v>336</v>
       </c>
@@ -9831,7 +10153,7 @@
         <v>45352</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="53" t="s">
         <v>337</v>
       </c>
@@ -9852,7 +10174,7 @@
         <v>43160</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="53" t="s">
         <v>338</v>
       </c>
@@ -9873,7 +10195,7 @@
         <v>44256</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="53" t="s">
         <v>339</v>
       </c>
@@ -9894,7 +10216,7 @@
         <v>43525</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="72" t="s">
         <v>340</v>
       </c>
@@ -9915,7 +10237,7 @@
         <v>43160</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="53" t="s">
         <v>341</v>
       </c>
@@ -9936,7 +10258,7 @@
         <v>44621</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="73" t="s">
         <v>342</v>
       </c>
@@ -9957,7 +10279,7 @@
         <v>43891</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="53" t="s">
         <v>343</v>
       </c>
@@ -9978,7 +10300,7 @@
         <v>44621</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="53" t="s">
         <v>344</v>
       </c>
@@ -9999,7 +10321,7 @@
         <v>43525</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="53" t="s">
         <v>345</v>
       </c>
@@ -10020,9 +10342,9 @@
         <v>45352</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="80" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B31" s="98">
         <v>20643500323</v>
@@ -10061,25 +10383,25 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:B15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="17.109375" customWidth="1"/>
+    <col min="2" max="2" width="17.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="104" t="s">
+    <row r="1" spans="1:2" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="108" t="s">
         <v>176</v>
       </c>
-      <c r="B1" s="105"/>
-    </row>
-    <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="106" t="s">
+      <c r="B1" s="109"/>
+    </row>
+    <row r="2" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="110" t="s">
         <v>177</v>
       </c>
-      <c r="B2" s="105"/>
-    </row>
-    <row r="3" spans="1:2" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="109"/>
+    </row>
+    <row r="3" spans="1:2" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>54</v>
       </c>
@@ -10087,7 +10409,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>56</v>
       </c>
@@ -10095,7 +10417,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>58</v>
       </c>
@@ -10103,7 +10425,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="23" t="s">
         <v>54</v>
       </c>
@@ -10111,7 +10433,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
         <v>346</v>
       </c>
@@ -10119,7 +10441,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
         <v>347</v>
       </c>
@@ -10127,7 +10449,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>348</v>
       </c>
@@ -10135,7 +10457,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>349</v>
       </c>
@@ -10143,7 +10465,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>350</v>
       </c>
@@ -10151,7 +10473,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>351</v>
       </c>
@@ -10159,7 +10481,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>352</v>
       </c>
@@ -10167,8 +10489,8 @@
         <v>185</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="14" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:B2"/>
@@ -10184,41 +10506,41 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:H16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="25.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.88671875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.85546875" hidden="1" customWidth="1"/>
     <col min="4" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="16" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="17" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="104" t="s">
+    <row r="1" spans="1:8" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="108" t="s">
         <v>186</v>
       </c>
-      <c r="B1" s="109"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
-      <c r="F1" s="105"/>
-      <c r="G1" s="105"/>
-      <c r="H1" s="105"/>
-    </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="106" t="s">
+      <c r="B1" s="113"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+      <c r="H1" s="109"/>
+    </row>
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="110" t="s">
         <v>187</v>
       </c>
-      <c r="B2" s="106"/>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
-      <c r="F2" s="105"/>
-      <c r="G2" s="105"/>
-      <c r="H2" s="105"/>
-    </row>
-    <row r="3" spans="1:8" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="110"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="109"/>
+      <c r="E2" s="109"/>
+      <c r="F2" s="109"/>
+      <c r="G2" s="109"/>
+      <c r="H2" s="109"/>
+    </row>
+    <row r="3" spans="1:8" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>54</v>
       </c>
@@ -10244,7 +10566,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>56</v>
       </c>
@@ -10270,7 +10592,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="20.399999999999999" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="22.5" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>58</v>
       </c>
@@ -10296,7 +10618,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="23" t="s">
         <v>54</v>
       </c>
@@ -10343,39 +10665,39 @@
       <c r="G7" s="3"/>
       <c r="H7" s="20"/>
     </row>
-    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G8" s="2"/>
       <c r="H8" s="21"/>
     </row>
-    <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G9" s="3"/>
       <c r="H9" s="20"/>
     </row>
-    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G10" s="2"/>
       <c r="H10" s="21"/>
     </row>
-    <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G11" s="3"/>
       <c r="H11" s="20"/>
     </row>
-    <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G12" s="2"/>
       <c r="H12" s="21"/>
     </row>
-    <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G13" s="3"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G14" s="2"/>
       <c r="H14" s="21"/>
     </row>
-    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G15" s="3"/>
       <c r="H15" s="20"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G16" s="27"/>
       <c r="H16" s="22"/>
     </row>
@@ -10399,40 +10721,40 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="36.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="104" t="s">
+    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="108" t="s">
         <v>207</v>
       </c>
-      <c r="B1" s="105"/>
-      <c r="C1" s="105"/>
-      <c r="D1" s="105"/>
-      <c r="E1" s="105"/>
-      <c r="F1" s="105"/>
-      <c r="G1" s="105"/>
-    </row>
-    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="106" t="s">
+      <c r="B1" s="109"/>
+      <c r="C1" s="109"/>
+      <c r="D1" s="109"/>
+      <c r="E1" s="109"/>
+      <c r="F1" s="109"/>
+      <c r="G1" s="109"/>
+    </row>
+    <row r="2" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="110" t="s">
         <v>208</v>
       </c>
-      <c r="B2" s="105"/>
-      <c r="C2" s="105"/>
-      <c r="D2" s="105"/>
-      <c r="E2" s="105"/>
-      <c r="F2" s="105"/>
-      <c r="G2" s="105"/>
-    </row>
-    <row r="3" spans="1:7" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="109"/>
+      <c r="C2" s="109"/>
+      <c r="D2" s="109"/>
+      <c r="E2" s="109"/>
+      <c r="F2" s="109"/>
+      <c r="G2" s="109"/>
+    </row>
+    <row r="3" spans="1:7" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>54</v>
       </c>
@@ -10455,7 +10777,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>56</v>
       </c>
@@ -10478,7 +10800,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="71.400000000000006" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="101.25" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>58</v>
       </c>
@@ -10501,7 +10823,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="23" t="s">
         <v>54</v>
       </c>
@@ -10524,7 +10846,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="34" t="s">
         <v>423</v>
       </c>
@@ -10548,7 +10870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
         <v>354</v>
       </c>
@@ -10572,7 +10894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>355</v>
       </c>
@@ -10596,7 +10918,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>356</v>
       </c>
@@ -10620,7 +10942,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>357</v>
       </c>
@@ -10644,7 +10966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="53" t="s">
         <v>358</v>
       </c>
@@ -10668,7 +10990,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>359</v>
       </c>
@@ -10692,7 +11014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="34" t="s">
         <v>360</v>
       </c>
@@ -10716,7 +11038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="59" t="s">
         <v>361</v>
       </c>
@@ -10740,7 +11062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="53" t="s">
         <v>362</v>
       </c>
@@ -10764,7 +11086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="53" t="s">
         <v>363</v>
       </c>
@@ -10788,7 +11110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
         <v>364</v>
       </c>
@@ -10812,7 +11134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>365</v>
       </c>
@@ -10836,7 +11158,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
         <v>366</v>
       </c>
@@ -10860,7 +11182,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="53" t="s">
         <v>367</v>
       </c>
@@ -10884,7 +11206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="80" t="s">
         <v>422</v>
       </c>
